--- a/research/traditional_assets/database/data/kenya/kenya_hotel_gaming.xlsx
+++ b/research/traditional_assets/database/data/kenya/kenya_hotel_gaming.xlsx
@@ -588,47 +588,50 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.187</v>
+        <v>-0.132</v>
       </c>
       <c r="G2">
-        <v>-0.1946859903381643</v>
+        <v>0.07162162162162163</v>
       </c>
       <c r="H2">
-        <v>-0.1946859903381643</v>
+        <v>0.07162162162162163</v>
       </c>
       <c r="I2">
-        <v>-0.4140096618357488</v>
+        <v>-0.1006756756756757</v>
       </c>
       <c r="J2">
-        <v>-0.4140096618357488</v>
+        <v>-0.1006756756756757</v>
       </c>
       <c r="K2">
-        <v>-10.5</v>
+        <v>-5.47</v>
       </c>
       <c r="L2">
-        <v>-0.5072463768115942</v>
+        <v>-0.1847972972972973</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.006</v>
       </c>
       <c r="N2">
-        <v>0</v>
+        <v>0.0003045685279187817</v>
       </c>
       <c r="O2">
-        <v>-0</v>
+        <v>-0.001096892138939671</v>
       </c>
       <c r="P2">
-        <v>0</v>
+        <v>0.006</v>
       </c>
       <c r="Q2">
-        <v>0</v>
+        <v>0.0003045685279187817</v>
       </c>
       <c r="R2">
-        <v>-0</v>
+        <v>-0.001096892138939671</v>
       </c>
       <c r="S2">
         <v>0</v>
       </c>
+      <c r="T2">
+        <v>0</v>
+      </c>
       <c r="U2">
         <v>0</v>
       </c>
@@ -636,10 +639,10 @@
         <v>0</v>
       </c>
       <c r="X2">
-        <v>0.1048781920643171</v>
+        <v>0.1542363249693662</v>
       </c>
       <c r="AB2">
-        <v>0.1048781920643171</v>
+        <v>0.1542363249693662</v>
       </c>
       <c r="AD2">
         <v>0</v>
@@ -660,22 +663,22 @@
         <v>0</v>
       </c>
       <c r="AL2">
-        <v>2.61</v>
+        <v>2.62</v>
       </c>
       <c r="AM2">
-        <v>2.505</v>
+        <v>2.582</v>
       </c>
       <c r="AN2">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AO2">
-        <v>-3.28352490421456</v>
+        <v>-1.137404580152672</v>
       </c>
       <c r="AP2">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AQ2">
-        <v>-3.421157684630739</v>
+        <v>-1.15414407436096</v>
       </c>
     </row>
     <row r="3">
@@ -695,47 +698,50 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.187</v>
+        <v>-0.132</v>
       </c>
       <c r="G3">
-        <v>-0.1946859903381643</v>
+        <v>0.07162162162162163</v>
       </c>
       <c r="H3">
-        <v>-0.1946859903381643</v>
+        <v>0.07162162162162163</v>
       </c>
       <c r="I3">
-        <v>-0.4140096618357488</v>
+        <v>-0.1006756756756757</v>
       </c>
       <c r="J3">
-        <v>-0.4140096618357488</v>
+        <v>-0.1006756756756757</v>
       </c>
       <c r="K3">
-        <v>-10.5</v>
+        <v>-5.47</v>
       </c>
       <c r="L3">
-        <v>-0.5072463768115942</v>
+        <v>-0.1847972972972973</v>
       </c>
       <c r="M3">
-        <v>-0</v>
+        <v>0.006</v>
       </c>
       <c r="N3">
-        <v>-0</v>
+        <v>0.0003045685279187817</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>-0.001096892138939671</v>
       </c>
       <c r="P3">
-        <v>-0</v>
+        <v>0.006</v>
       </c>
       <c r="Q3">
-        <v>-0</v>
+        <v>0.0003045685279187817</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>-0.001096892138939671</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
+      <c r="T3">
+        <v>0</v>
+      </c>
       <c r="U3">
         <v>0</v>
       </c>
@@ -743,10 +749,10 @@
         <v>0</v>
       </c>
       <c r="X3">
-        <v>0.1048781920643171</v>
+        <v>0.1542363249693662</v>
       </c>
       <c r="AB3">
-        <v>0.1048781920643171</v>
+        <v>0.1542363249693662</v>
       </c>
       <c r="AD3">
         <v>0</v>
@@ -767,22 +773,22 @@
         <v>0</v>
       </c>
       <c r="AL3">
-        <v>2.61</v>
+        <v>2.62</v>
       </c>
       <c r="AM3">
-        <v>2.505</v>
+        <v>2.582</v>
       </c>
       <c r="AN3">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AO3">
-        <v>-3.28352490421456</v>
+        <v>-1.137404580152672</v>
       </c>
       <c r="AP3">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AQ3">
-        <v>-3.421157684630739</v>
+        <v>-1.15414407436096</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/kenya/kenya_hotel_gaming.xlsx
+++ b/research/traditional_assets/database/data/kenya/kenya_hotel_gaming.xlsx
@@ -8,6 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="earnings_debt" sheetId="1" r:id="rId1"/>
+    <sheet name="cost_capital" sheetId="2" r:id="rId2"/>
+    <sheet name="nase_tpse" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -588,43 +590,46 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.132</v>
+        <v>0.0122</v>
+      </c>
+      <c r="E2">
+        <v>0.389</v>
       </c>
       <c r="G2">
-        <v>0.07162162162162163</v>
+        <v>0.2643478260869565</v>
       </c>
       <c r="H2">
-        <v>0.07162162162162163</v>
+        <v>0.2643478260869565</v>
       </c>
       <c r="I2">
-        <v>-0.1006756756756757</v>
+        <v>0.1843478260869565</v>
       </c>
       <c r="J2">
-        <v>-0.1006756756756757</v>
+        <v>0.1030870357171141</v>
       </c>
       <c r="K2">
-        <v>-5.47</v>
+        <v>2.74</v>
       </c>
       <c r="L2">
-        <v>-0.1847972972972973</v>
+        <v>0.04765217391304348</v>
       </c>
       <c r="M2">
-        <v>0.006</v>
+        <v>0.015</v>
       </c>
       <c r="N2">
-        <v>0.0003045685279187817</v>
+        <v>0.0005050505050505051</v>
       </c>
       <c r="O2">
-        <v>-0.001096892138939671</v>
+        <v>0.005474452554744525</v>
       </c>
       <c r="P2">
-        <v>0.006</v>
+        <v>0.015</v>
       </c>
       <c r="Q2">
-        <v>0.0003045685279187817</v>
+        <v>0.0005050505050505051</v>
       </c>
       <c r="R2">
-        <v>-0.001096892138939671</v>
+        <v>0.005474452554744525</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -639,10 +644,10 @@
         <v>0</v>
       </c>
       <c r="X2">
-        <v>0.1542363249693662</v>
+        <v>0.1443169501904196</v>
       </c>
       <c r="AB2">
-        <v>0.1542363249693662</v>
+        <v>0.1443169501904196</v>
       </c>
       <c r="AD2">
         <v>0</v>
@@ -663,22 +668,22 @@
         <v>0</v>
       </c>
       <c r="AL2">
-        <v>2.62</v>
+        <v>2.33</v>
       </c>
       <c r="AM2">
-        <v>2.582</v>
+        <v>2.224</v>
       </c>
       <c r="AN2">
         <v>0</v>
       </c>
       <c r="AO2">
-        <v>-1.137404580152672</v>
+        <v>4.549356223175965</v>
       </c>
       <c r="AP2">
         <v>0</v>
       </c>
       <c r="AQ2">
-        <v>-1.15414407436096</v>
+        <v>4.766187050359711</v>
       </c>
     </row>
     <row r="3">
@@ -698,43 +703,46 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.132</v>
+        <v>0.0122</v>
+      </c>
+      <c r="E3">
+        <v>0.389</v>
       </c>
       <c r="G3">
-        <v>0.07162162162162163</v>
+        <v>0.2643478260869565</v>
       </c>
       <c r="H3">
-        <v>0.07162162162162163</v>
+        <v>0.2643478260869565</v>
       </c>
       <c r="I3">
-        <v>-0.1006756756756757</v>
+        <v>0.1843478260869565</v>
       </c>
       <c r="J3">
-        <v>-0.1006756756756757</v>
+        <v>0.1030870357171141</v>
       </c>
       <c r="K3">
-        <v>-5.47</v>
+        <v>2.74</v>
       </c>
       <c r="L3">
-        <v>-0.1847972972972973</v>
+        <v>0.04765217391304348</v>
       </c>
       <c r="M3">
-        <v>0.006</v>
+        <v>0.015</v>
       </c>
       <c r="N3">
-        <v>0.0003045685279187817</v>
+        <v>0.0005050505050505051</v>
       </c>
       <c r="O3">
-        <v>-0.001096892138939671</v>
+        <v>0.005474452554744525</v>
       </c>
       <c r="P3">
-        <v>0.006</v>
+        <v>0.015</v>
       </c>
       <c r="Q3">
-        <v>0.0003045685279187817</v>
+        <v>0.0005050505050505051</v>
       </c>
       <c r="R3">
-        <v>-0.001096892138939671</v>
+        <v>0.005474452554744525</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -749,10 +757,10 @@
         <v>0</v>
       </c>
       <c r="X3">
-        <v>0.1542363249693662</v>
+        <v>0.1443169501904196</v>
       </c>
       <c r="AB3">
-        <v>0.1542363249693662</v>
+        <v>0.1443169501904196</v>
       </c>
       <c r="AD3">
         <v>0</v>
@@ -773,22 +781,8791 @@
         <v>0</v>
       </c>
       <c r="AL3">
-        <v>2.62</v>
+        <v>2.33</v>
       </c>
       <c r="AM3">
-        <v>2.582</v>
+        <v>2.224</v>
       </c>
       <c r="AN3">
         <v>0</v>
       </c>
       <c r="AO3">
-        <v>-1.137404580152672</v>
+        <v>4.549356223175965</v>
       </c>
       <c r="AP3">
         <v>0</v>
       </c>
       <c r="AQ3">
-        <v>-1.15414407436096</v>
+        <v>4.766187050359711</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:AY2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>company_name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>exchange_ticker</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>industry_group</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>current_interest_coverage</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_interest_coverage</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt_ebitda</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_ebitda</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt_capital</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_capital</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>current_equity_value</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_equity_value</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>current_enterprise_value</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_enterprise_value</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>current_cost_capital</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_capital</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>current_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt_rating</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_rating</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>current_cost_equity</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_equity</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>current_beta</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_beta</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_mv_debt</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_coverage_ratio</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_debt</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_interest_expense</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_depreciation</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_ebitda</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>country_default_spread</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>risk_free</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>market_capitalization</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_risk_premium</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>reported_debt_rating</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>marginal_tax_rate</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_max_percentage</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_method</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_drop_ebitda</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>reported_capital_spending</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>reported_interest_expense</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>reported_bv_debt</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>reported_cash</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_ev_implied_growth</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>flag_bankruptcy</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>flag_refinanced</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>rating_firm_type</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio_limit</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>TPS Eastern Africa Plc (NASE:TPSE)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>NASE:TPSE</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Hotel/Gaming</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Kenya</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>4.3862660944206</v>
+      </c>
+      <c r="F2">
+        <v>7.02189050316792</v>
+      </c>
+      <c r="G2">
+        <v>0</v>
+      </c>
+      <c r="H2">
+        <v>1.93440789473684</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>0.99</v>
+      </c>
+      <c r="K2">
+        <v>29.7</v>
+      </c>
+      <c r="L2">
+        <v>4.51061430402365</v>
+      </c>
+      <c r="M2">
+        <v>29.7</v>
+      </c>
+      <c r="N2">
+        <v>33.9136143040237</v>
+      </c>
+      <c r="O2">
+        <v>0</v>
+      </c>
+      <c r="P2">
+        <v>29.403</v>
+      </c>
+      <c r="Q2">
+        <v>0.14431695019042</v>
+      </c>
+      <c r="R2">
+        <v>0.108869915983865</v>
+      </c>
+      <c r="S2">
+        <v>0.08516459296222829</v>
+      </c>
+      <c r="T2">
+        <v>0.03465</v>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="W2">
+        <v>0.14431695019042</v>
+      </c>
+      <c r="X2">
+        <v>7.45664159838649</v>
+      </c>
+      <c r="Y2">
+        <v>0.7480479046815171</v>
+      </c>
+      <c r="Z2">
+        <v>52.5877676991106</v>
+      </c>
+      <c r="AA2">
+        <v>0</v>
+      </c>
+      <c r="AB2">
+        <v>0.1216637042317547</v>
+      </c>
+      <c r="AC2">
+        <v>4.3862660944206</v>
+      </c>
+      <c r="AD2">
+        <v>0</v>
+      </c>
+      <c r="AE2">
+        <v>2.33</v>
+      </c>
+      <c r="AF2">
+        <v>4.98</v>
+      </c>
+      <c r="AG2">
+        <v>15.2</v>
+      </c>
+      <c r="AH2">
+        <v>0</v>
+      </c>
+      <c r="AI2">
+        <v>0.0388</v>
+      </c>
+      <c r="AJ2">
+        <v>29.7</v>
+      </c>
+      <c r="AK2">
+        <v>0.1410564076579343</v>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="AM2">
+        <v>0.3</v>
+      </c>
+      <c r="AN2">
+        <v>0</v>
+      </c>
+      <c r="AO2">
+        <v>2</v>
+      </c>
+      <c r="AQ2">
+        <v>2.27</v>
+      </c>
+      <c r="AR2">
+        <v>2.33</v>
+      </c>
+      <c r="AT2">
+        <v>0</v>
+      </c>
+      <c r="AV2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AW2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AX2">
+        <v>1</v>
+      </c>
+      <c r="AY2">
+        <v>10000000</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:Z101"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>debt_capital</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>cost_capital</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>equity_value</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>enterprise_value</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>debt_issued</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>debt</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>marketcap</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>drop_ebitda</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ebitda</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>depreciation</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ebit</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>interest_expense</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>taxable_income</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>taxes</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>net_income</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>operating_cash_flow</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>debt_equity</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>beta</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>tax_rate</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>debt_rating</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>0.1443169501904196</v>
+      </c>
+      <c r="C2">
+        <v>29.7</v>
+      </c>
+      <c r="D2">
+        <v>29.7</v>
+      </c>
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>0</v>
+      </c>
+      <c r="H2">
+        <v>29.7</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>15.2</v>
+      </c>
+      <c r="K2">
+        <v>4.98</v>
+      </c>
+      <c r="L2">
+        <v>10.22</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>10.22</v>
+      </c>
+      <c r="O2">
+        <v>3.065999999999999</v>
+      </c>
+      <c r="P2">
+        <v>7.154</v>
+      </c>
+      <c r="Q2">
+        <v>12.134</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="S2">
+        <v>0.1443169501904196</v>
+      </c>
+      <c r="T2">
+        <v>0.7480479046815168</v>
+      </c>
+      <c r="U2">
+        <v>0.0447</v>
+      </c>
+      <c r="V2">
+        <v>0.3</v>
+      </c>
+      <c r="W2">
+        <v>0.03129</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y2">
+        <v>10000000</v>
+      </c>
+      <c r="Z2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>0.01</v>
+      </c>
+      <c r="B3">
+        <v>0.1439252993398484</v>
+      </c>
+      <c r="C3">
+        <v>29.44382751254373</v>
+      </c>
+      <c r="D3">
+        <v>29.74082751254373</v>
+      </c>
+      <c r="E3">
+        <v>0.297</v>
+      </c>
+      <c r="F3">
+        <v>0.297</v>
+      </c>
+      <c r="G3">
+        <v>0</v>
+      </c>
+      <c r="H3">
+        <v>29.7</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>15.2</v>
+      </c>
+      <c r="K3">
+        <v>4.98</v>
+      </c>
+      <c r="L3">
+        <v>10.22</v>
+      </c>
+      <c r="M3">
+        <v>0.0132759</v>
+      </c>
+      <c r="N3">
+        <v>10.2067241</v>
+      </c>
+      <c r="O3">
+        <v>3.062017229999999</v>
+      </c>
+      <c r="P3">
+        <v>7.144706869999999</v>
+      </c>
+      <c r="Q3">
+        <v>12.12470687</v>
+      </c>
+      <c r="R3">
+        <v>0.0101010101010101</v>
+      </c>
+      <c r="S3">
+        <v>0.1450630296362105</v>
+      </c>
+      <c r="T3">
+        <v>0.753337132290376</v>
+      </c>
+      <c r="U3">
+        <v>0.0447</v>
+      </c>
+      <c r="V3">
+        <v>0.3</v>
+      </c>
+      <c r="W3">
+        <v>0.03129</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y3">
+        <v>769.8159823439464</v>
+      </c>
+      <c r="Z3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>0.02</v>
+      </c>
+      <c r="B4">
+        <v>0.1435336484892771</v>
+      </c>
+      <c r="C4">
+        <v>29.18776742780411</v>
+      </c>
+      <c r="D4">
+        <v>29.78176742780411</v>
+      </c>
+      <c r="E4">
+        <v>0.594</v>
+      </c>
+      <c r="F4">
+        <v>0.594</v>
+      </c>
+      <c r="G4">
+        <v>0</v>
+      </c>
+      <c r="H4">
+        <v>29.7</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>15.2</v>
+      </c>
+      <c r="K4">
+        <v>4.98</v>
+      </c>
+      <c r="L4">
+        <v>10.22</v>
+      </c>
+      <c r="M4">
+        <v>0.0265518</v>
+      </c>
+      <c r="N4">
+        <v>10.1934482</v>
+      </c>
+      <c r="O4">
+        <v>3.05803446</v>
+      </c>
+      <c r="P4">
+        <v>7.135413739999999</v>
+      </c>
+      <c r="Q4">
+        <v>12.11541374</v>
+      </c>
+      <c r="R4">
+        <v>0.02040816326530612</v>
+      </c>
+      <c r="S4">
+        <v>0.1458243351931399</v>
+      </c>
+      <c r="T4">
+        <v>0.7587343033198242</v>
+      </c>
+      <c r="U4">
+        <v>0.0447</v>
+      </c>
+      <c r="V4">
+        <v>0.3</v>
+      </c>
+      <c r="W4">
+        <v>0.03129</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y4">
+        <v>384.9079911719732</v>
+      </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>0.03</v>
+      </c>
+      <c r="B5">
+        <v>0.1431419976387058</v>
+      </c>
+      <c r="C5">
+        <v>28.93182021060691</v>
+      </c>
+      <c r="D5">
+        <v>29.82282021060691</v>
+      </c>
+      <c r="E5">
+        <v>0.8909999999999999</v>
+      </c>
+      <c r="F5">
+        <v>0.8909999999999999</v>
+      </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5">
+        <v>29.7</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>15.2</v>
+      </c>
+      <c r="K5">
+        <v>4.98</v>
+      </c>
+      <c r="L5">
+        <v>10.22</v>
+      </c>
+      <c r="M5">
+        <v>0.0398277</v>
+      </c>
+      <c r="N5">
+        <v>10.1801723</v>
+      </c>
+      <c r="O5">
+        <v>3.05405169</v>
+      </c>
+      <c r="P5">
+        <v>7.126120609999999</v>
+      </c>
+      <c r="Q5">
+        <v>12.10612061</v>
+      </c>
+      <c r="R5">
+        <v>0.03092783505154639</v>
+      </c>
+      <c r="S5">
+        <v>0.1466013377718617</v>
+      </c>
+      <c r="T5">
+        <v>0.7642427562261682</v>
+      </c>
+      <c r="U5">
+        <v>0.0447</v>
+      </c>
+      <c r="V5">
+        <v>0.3</v>
+      </c>
+      <c r="W5">
+        <v>0.03129</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y5">
+        <v>256.6053274479822</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>0.04</v>
+      </c>
+      <c r="B6">
+        <v>0.1427503467881346</v>
+      </c>
+      <c r="C6">
+        <v>28.67598632834439</v>
+      </c>
+      <c r="D6">
+        <v>29.86398632834439</v>
+      </c>
+      <c r="E6">
+        <v>1.188</v>
+      </c>
+      <c r="F6">
+        <v>1.188</v>
+      </c>
+      <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6">
+        <v>29.7</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>15.2</v>
+      </c>
+      <c r="K6">
+        <v>4.98</v>
+      </c>
+      <c r="L6">
+        <v>10.22</v>
+      </c>
+      <c r="M6">
+        <v>0.0531036</v>
+      </c>
+      <c r="N6">
+        <v>10.1668964</v>
+      </c>
+      <c r="O6">
+        <v>3.05006892</v>
+      </c>
+      <c r="P6">
+        <v>7.11682748</v>
+      </c>
+      <c r="Q6">
+        <v>12.09682748</v>
+      </c>
+      <c r="R6">
+        <v>0.04166666666666667</v>
+      </c>
+      <c r="S6">
+        <v>0.1473945279043068</v>
+      </c>
+      <c r="T6">
+        <v>0.769865968568061</v>
+      </c>
+      <c r="U6">
+        <v>0.0447</v>
+      </c>
+      <c r="V6">
+        <v>0.3</v>
+      </c>
+      <c r="W6">
+        <v>0.03129</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y6">
+        <v>192.4539955859866</v>
+      </c>
+      <c r="Z6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>0.05</v>
+      </c>
+      <c r="B7">
+        <v>0.1423586959375633</v>
+      </c>
+      <c r="C7">
+        <v>28.42026625099305</v>
+      </c>
+      <c r="D7">
+        <v>29.90526625099305</v>
+      </c>
+      <c r="E7">
+        <v>1.485</v>
+      </c>
+      <c r="F7">
+        <v>1.485</v>
+      </c>
+      <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7">
+        <v>29.7</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>15.2</v>
+      </c>
+      <c r="K7">
+        <v>4.98</v>
+      </c>
+      <c r="L7">
+        <v>10.22</v>
+      </c>
+      <c r="M7">
+        <v>0.06637950000000001</v>
+      </c>
+      <c r="N7">
+        <v>10.1536205</v>
+      </c>
+      <c r="O7">
+        <v>3.046086149999999</v>
+      </c>
+      <c r="P7">
+        <v>7.10753435</v>
+      </c>
+      <c r="Q7">
+        <v>12.08753435</v>
+      </c>
+      <c r="R7">
+        <v>0.05263157894736843</v>
+      </c>
+      <c r="S7">
+        <v>0.1482044167763824</v>
+      </c>
+      <c r="T7">
+        <v>0.7756075643276779</v>
+      </c>
+      <c r="U7">
+        <v>0.0447</v>
+      </c>
+      <c r="V7">
+        <v>0.3</v>
+      </c>
+      <c r="W7">
+        <v>0.03129</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y7">
+        <v>153.9631964687893</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>0.06</v>
+      </c>
+      <c r="B8">
+        <v>0.1419670450869921</v>
+      </c>
+      <c r="C8">
+        <v>28.16466045113154</v>
+      </c>
+      <c r="D8">
+        <v>29.94666045113154</v>
+      </c>
+      <c r="E8">
+        <v>1.782</v>
+      </c>
+      <c r="F8">
+        <v>1.782</v>
+      </c>
+      <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8">
+        <v>29.7</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>15.2</v>
+      </c>
+      <c r="K8">
+        <v>4.98</v>
+      </c>
+      <c r="L8">
+        <v>10.22</v>
+      </c>
+      <c r="M8">
+        <v>0.0796554</v>
+      </c>
+      <c r="N8">
+        <v>10.1403446</v>
+      </c>
+      <c r="O8">
+        <v>3.042103379999999</v>
+      </c>
+      <c r="P8">
+        <v>7.098241219999999</v>
+      </c>
+      <c r="Q8">
+        <v>12.07824122</v>
+      </c>
+      <c r="R8">
+        <v>0.06382978723404255</v>
+      </c>
+      <c r="S8">
+        <v>0.1490315373265873</v>
+      </c>
+      <c r="T8">
+        <v>0.7814713216992015</v>
+      </c>
+      <c r="U8">
+        <v>0.0447</v>
+      </c>
+      <c r="V8">
+        <v>0.3</v>
+      </c>
+      <c r="W8">
+        <v>0.03129</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y8">
+        <v>128.3026637239911</v>
+      </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="B9">
+        <v>0.1415753942364208</v>
+      </c>
+      <c r="C9">
+        <v>27.90916940395864</v>
+      </c>
+      <c r="D9">
+        <v>29.98816940395864</v>
+      </c>
+      <c r="E9">
+        <v>2.079</v>
+      </c>
+      <c r="F9">
+        <v>2.079</v>
+      </c>
+      <c r="G9">
+        <v>0</v>
+      </c>
+      <c r="H9">
+        <v>29.7</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>15.2</v>
+      </c>
+      <c r="K9">
+        <v>4.98</v>
+      </c>
+      <c r="L9">
+        <v>10.22</v>
+      </c>
+      <c r="M9">
+        <v>0.09293130000000002</v>
+      </c>
+      <c r="N9">
+        <v>10.1270687</v>
+      </c>
+      <c r="O9">
+        <v>3.03812061</v>
+      </c>
+      <c r="P9">
+        <v>7.088948089999999</v>
+      </c>
+      <c r="Q9">
+        <v>12.06894809</v>
+      </c>
+      <c r="R9">
+        <v>0.07526881720430109</v>
+      </c>
+      <c r="S9">
+        <v>0.1498764454155063</v>
+      </c>
+      <c r="T9">
+        <v>0.7874611813797904</v>
+      </c>
+      <c r="U9">
+        <v>0.0447</v>
+      </c>
+      <c r="V9">
+        <v>0.3</v>
+      </c>
+      <c r="W9">
+        <v>0.03129</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y9">
+        <v>109.9737117634209</v>
+      </c>
+      <c r="Z9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>0.08</v>
+      </c>
+      <c r="B10">
+        <v>0.1411837433858496</v>
+      </c>
+      <c r="C10">
+        <v>27.65379358731148</v>
+      </c>
+      <c r="D10">
+        <v>30.02979358731148</v>
+      </c>
+      <c r="E10">
+        <v>2.376</v>
+      </c>
+      <c r="F10">
+        <v>2.376</v>
+      </c>
+      <c r="G10">
+        <v>0</v>
+      </c>
+      <c r="H10">
+        <v>29.7</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>15.2</v>
+      </c>
+      <c r="K10">
+        <v>4.98</v>
+      </c>
+      <c r="L10">
+        <v>10.22</v>
+      </c>
+      <c r="M10">
+        <v>0.1062072</v>
+      </c>
+      <c r="N10">
+        <v>10.1137928</v>
+      </c>
+      <c r="O10">
+        <v>3.03413784</v>
+      </c>
+      <c r="P10">
+        <v>7.079654959999999</v>
+      </c>
+      <c r="Q10">
+        <v>12.05965496</v>
+      </c>
+      <c r="R10">
+        <v>0.08695652173913043</v>
+      </c>
+      <c r="S10">
+        <v>0.1507397210715756</v>
+      </c>
+      <c r="T10">
+        <v>0.7935812554012615</v>
+      </c>
+      <c r="U10">
+        <v>0.0447</v>
+      </c>
+      <c r="V10">
+        <v>0.3</v>
+      </c>
+      <c r="W10">
+        <v>0.03129</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y10">
+        <v>96.2269977929933</v>
+      </c>
+      <c r="Z10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>0.09</v>
+      </c>
+      <c r="B11">
+        <v>0.1407920925352783</v>
+      </c>
+      <c r="C11">
+        <v>27.39853348168389</v>
+      </c>
+      <c r="D11">
+        <v>30.07153348168389</v>
+      </c>
+      <c r="E11">
+        <v>2.673</v>
+      </c>
+      <c r="F11">
+        <v>2.673</v>
+      </c>
+      <c r="G11">
+        <v>0</v>
+      </c>
+      <c r="H11">
+        <v>29.7</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>15.2</v>
+      </c>
+      <c r="K11">
+        <v>4.98</v>
+      </c>
+      <c r="L11">
+        <v>10.22</v>
+      </c>
+      <c r="M11">
+        <v>0.1194831</v>
+      </c>
+      <c r="N11">
+        <v>10.1005169</v>
+      </c>
+      <c r="O11">
+        <v>3.03015507</v>
+      </c>
+      <c r="P11">
+        <v>7.07036183</v>
+      </c>
+      <c r="Q11">
+        <v>12.05036183</v>
+      </c>
+      <c r="R11">
+        <v>0.0989010989010989</v>
+      </c>
+      <c r="S11">
+        <v>0.1516219698189872</v>
+      </c>
+      <c r="T11">
+        <v>0.7998358365440834</v>
+      </c>
+      <c r="U11">
+        <v>0.0447</v>
+      </c>
+      <c r="V11">
+        <v>0.3</v>
+      </c>
+      <c r="W11">
+        <v>0.03129</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y11">
+        <v>85.53510914932738</v>
+      </c>
+      <c r="Z11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>0.1</v>
+      </c>
+      <c r="B12">
+        <v>0.140400441684707</v>
+      </c>
+      <c r="C12">
+        <v>27.14338957024481</v>
+      </c>
+      <c r="D12">
+        <v>30.11338957024481</v>
+      </c>
+      <c r="E12">
+        <v>2.97</v>
+      </c>
+      <c r="F12">
+        <v>2.97</v>
+      </c>
+      <c r="G12">
+        <v>0</v>
+      </c>
+      <c r="H12">
+        <v>29.7</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>15.2</v>
+      </c>
+      <c r="K12">
+        <v>4.98</v>
+      </c>
+      <c r="L12">
+        <v>10.22</v>
+      </c>
+      <c r="M12">
+        <v>0.132759</v>
+      </c>
+      <c r="N12">
+        <v>10.087241</v>
+      </c>
+      <c r="O12">
+        <v>3.026172299999999</v>
+      </c>
+      <c r="P12">
+        <v>7.0610687</v>
+      </c>
+      <c r="Q12">
+        <v>12.0410687</v>
+      </c>
+      <c r="R12">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="S12">
+        <v>0.1525238240941189</v>
+      </c>
+      <c r="T12">
+        <v>0.8062294083789681</v>
+      </c>
+      <c r="U12">
+        <v>0.0447</v>
+      </c>
+      <c r="V12">
+        <v>0.3</v>
+      </c>
+      <c r="W12">
+        <v>0.03129</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y12">
+        <v>76.98159823439464</v>
+      </c>
+      <c r="Z12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>0.11</v>
+      </c>
+      <c r="B13">
+        <v>0.1400087908341358</v>
+      </c>
+      <c r="C13">
+        <v>26.88836233885706</v>
+      </c>
+      <c r="D13">
+        <v>30.15536233885706</v>
+      </c>
+      <c r="E13">
+        <v>3.267</v>
+      </c>
+      <c r="F13">
+        <v>3.267</v>
+      </c>
+      <c r="G13">
+        <v>0</v>
+      </c>
+      <c r="H13">
+        <v>29.7</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>15.2</v>
+      </c>
+      <c r="K13">
+        <v>4.98</v>
+      </c>
+      <c r="L13">
+        <v>10.22</v>
+      </c>
+      <c r="M13">
+        <v>0.1460349</v>
+      </c>
+      <c r="N13">
+        <v>10.0739651</v>
+      </c>
+      <c r="O13">
+        <v>3.022189529999999</v>
+      </c>
+      <c r="P13">
+        <v>7.051775569999999</v>
+      </c>
+      <c r="Q13">
+        <v>12.03177557</v>
+      </c>
+      <c r="R13">
+        <v>0.1235955056179775</v>
+      </c>
+      <c r="S13">
+        <v>0.1534459447574559</v>
+      </c>
+      <c r="T13">
+        <v>0.8127666559854233</v>
+      </c>
+      <c r="U13">
+        <v>0.0447</v>
+      </c>
+      <c r="V13">
+        <v>0.3</v>
+      </c>
+      <c r="W13">
+        <v>0.03129</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y13">
+        <v>69.98327112217696</v>
+      </c>
+      <c r="Z13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>0.12</v>
+      </c>
+      <c r="B14">
+        <v>0.1396171399835645</v>
+      </c>
+      <c r="C14">
+        <v>26.63345227609602</v>
+      </c>
+      <c r="D14">
+        <v>30.19745227609602</v>
+      </c>
+      <c r="E14">
+        <v>3.564</v>
+      </c>
+      <c r="F14">
+        <v>3.564</v>
+      </c>
+      <c r="G14">
+        <v>0</v>
+      </c>
+      <c r="H14">
+        <v>29.7</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>15.2</v>
+      </c>
+      <c r="K14">
+        <v>4.98</v>
+      </c>
+      <c r="L14">
+        <v>10.22</v>
+      </c>
+      <c r="M14">
+        <v>0.1593108</v>
+      </c>
+      <c r="N14">
+        <v>10.0606892</v>
+      </c>
+      <c r="O14">
+        <v>3.01820676</v>
+      </c>
+      <c r="P14">
+        <v>7.042482439999999</v>
+      </c>
+      <c r="Q14">
+        <v>12.02248244</v>
+      </c>
+      <c r="R14">
+        <v>0.1363636363636364</v>
+      </c>
+      <c r="S14">
+        <v>0.1543890227085961</v>
+      </c>
+      <c r="T14">
+        <v>0.8194524774011162</v>
+      </c>
+      <c r="U14">
+        <v>0.0447</v>
+      </c>
+      <c r="V14">
+        <v>0.3</v>
+      </c>
+      <c r="W14">
+        <v>0.03129</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y14">
+        <v>64.15133186199554</v>
+      </c>
+      <c r="Z14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>0.13</v>
+      </c>
+      <c r="B15">
+        <v>0.1392254891329933</v>
+      </c>
+      <c r="C15">
+        <v>26.37865987326865</v>
+      </c>
+      <c r="D15">
+        <v>30.23965987326865</v>
+      </c>
+      <c r="E15">
+        <v>3.861</v>
+      </c>
+      <c r="F15">
+        <v>3.861</v>
+      </c>
+      <c r="G15">
+        <v>0</v>
+      </c>
+      <c r="H15">
+        <v>29.7</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>15.2</v>
+      </c>
+      <c r="K15">
+        <v>4.98</v>
+      </c>
+      <c r="L15">
+        <v>10.22</v>
+      </c>
+      <c r="M15">
+        <v>0.1725867</v>
+      </c>
+      <c r="N15">
+        <v>10.0474133</v>
+      </c>
+      <c r="O15">
+        <v>3.01422399</v>
+      </c>
+      <c r="P15">
+        <v>7.033189309999999</v>
+      </c>
+      <c r="Q15">
+        <v>12.01318931</v>
+      </c>
+      <c r="R15">
+        <v>0.1494252873563219</v>
+      </c>
+      <c r="S15">
+        <v>0.1553537806126359</v>
+      </c>
+      <c r="T15">
+        <v>0.8262919958608479</v>
+      </c>
+      <c r="U15">
+        <v>0.0447</v>
+      </c>
+      <c r="V15">
+        <v>0.3</v>
+      </c>
+      <c r="W15">
+        <v>0.03129</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y15">
+        <v>59.21661402645741</v>
+      </c>
+      <c r="Z15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>0.14</v>
+      </c>
+      <c r="B16">
+        <v>0.138833838282422</v>
+      </c>
+      <c r="C16">
+        <v>26.12398562443261</v>
+      </c>
+      <c r="D16">
+        <v>30.28198562443261</v>
+      </c>
+      <c r="E16">
+        <v>4.158</v>
+      </c>
+      <c r="F16">
+        <v>4.158</v>
+      </c>
+      <c r="G16">
+        <v>0</v>
+      </c>
+      <c r="H16">
+        <v>29.7</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>15.2</v>
+      </c>
+      <c r="K16">
+        <v>4.98</v>
+      </c>
+      <c r="L16">
+        <v>10.22</v>
+      </c>
+      <c r="M16">
+        <v>0.1858626</v>
+      </c>
+      <c r="N16">
+        <v>10.0341374</v>
+      </c>
+      <c r="O16">
+        <v>3.01024122</v>
+      </c>
+      <c r="P16">
+        <v>7.023896179999999</v>
+      </c>
+      <c r="Q16">
+        <v>12.00389618</v>
+      </c>
+      <c r="R16">
+        <v>0.1627906976744186</v>
+      </c>
+      <c r="S16">
+        <v>0.1563409747470023</v>
+      </c>
+      <c r="T16">
+        <v>0.8332905728894106</v>
+      </c>
+      <c r="U16">
+        <v>0.0447</v>
+      </c>
+      <c r="V16">
+        <v>0.3</v>
+      </c>
+      <c r="W16">
+        <v>0.03129</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y16">
+        <v>54.98685588171045</v>
+      </c>
+      <c r="Z16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>0.15</v>
+      </c>
+      <c r="B17">
+        <v>0.1384421874318507</v>
+      </c>
+      <c r="C17">
+        <v>25.86943002641551</v>
+      </c>
+      <c r="D17">
+        <v>30.32443002641551</v>
+      </c>
+      <c r="E17">
+        <v>4.455</v>
+      </c>
+      <c r="F17">
+        <v>4.455</v>
+      </c>
+      <c r="G17">
+        <v>0</v>
+      </c>
+      <c r="H17">
+        <v>29.7</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>15.2</v>
+      </c>
+      <c r="K17">
+        <v>4.98</v>
+      </c>
+      <c r="L17">
+        <v>10.22</v>
+      </c>
+      <c r="M17">
+        <v>0.1991385</v>
+      </c>
+      <c r="N17">
+        <v>10.0208615</v>
+      </c>
+      <c r="O17">
+        <v>3.006258449999999</v>
+      </c>
+      <c r="P17">
+        <v>7.01460305</v>
+      </c>
+      <c r="Q17">
+        <v>11.99460305</v>
+      </c>
+      <c r="R17">
+        <v>0.1764705882352941</v>
+      </c>
+      <c r="S17">
+        <v>0.1573513969786479</v>
+      </c>
+      <c r="T17">
+        <v>0.8404538223186454</v>
+      </c>
+      <c r="U17">
+        <v>0.0447</v>
+      </c>
+      <c r="V17">
+        <v>0.3</v>
+      </c>
+      <c r="W17">
+        <v>0.03129</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y17">
+        <v>51.32106548959642</v>
+      </c>
+      <c r="Z17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>0.16</v>
+      </c>
+      <c r="B18">
+        <v>0.1380505365812795</v>
+      </c>
+      <c r="C18">
+        <v>25.61499357883434</v>
+      </c>
+      <c r="D18">
+        <v>30.36699357883434</v>
+      </c>
+      <c r="E18">
+        <v>4.752</v>
+      </c>
+      <c r="F18">
+        <v>4.752</v>
+      </c>
+      <c r="G18">
+        <v>0</v>
+      </c>
+      <c r="H18">
+        <v>29.7</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>15.2</v>
+      </c>
+      <c r="K18">
+        <v>4.98</v>
+      </c>
+      <c r="L18">
+        <v>10.22</v>
+      </c>
+      <c r="M18">
+        <v>0.2124144</v>
+      </c>
+      <c r="N18">
+        <v>10.0075856</v>
+      </c>
+      <c r="O18">
+        <v>3.002275679999999</v>
+      </c>
+      <c r="P18">
+        <v>7.005309919999999</v>
+      </c>
+      <c r="Q18">
+        <v>11.98530992</v>
+      </c>
+      <c r="R18">
+        <v>0.1904761904761905</v>
+      </c>
+      <c r="S18">
+        <v>0.1583858768824756</v>
+      </c>
+      <c r="T18">
+        <v>0.8477876253057191</v>
+      </c>
+      <c r="U18">
+        <v>0.0447</v>
+      </c>
+      <c r="V18">
+        <v>0.3</v>
+      </c>
+      <c r="W18">
+        <v>0.03129</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y18">
+        <v>48.11349889649665</v>
+      </c>
+      <c r="Z18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>0.17</v>
+      </c>
+      <c r="B19">
+        <v>0.1376588857307082</v>
+      </c>
+      <c r="C19">
+        <v>25.36067678411513</v>
+      </c>
+      <c r="D19">
+        <v>30.40967678411513</v>
+      </c>
+      <c r="E19">
+        <v>5.049</v>
+      </c>
+      <c r="F19">
+        <v>5.049</v>
+      </c>
+      <c r="G19">
+        <v>0</v>
+      </c>
+      <c r="H19">
+        <v>29.7</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>15.2</v>
+      </c>
+      <c r="K19">
+        <v>4.98</v>
+      </c>
+      <c r="L19">
+        <v>10.22</v>
+      </c>
+      <c r="M19">
+        <v>0.2256903</v>
+      </c>
+      <c r="N19">
+        <v>9.994309699999999</v>
+      </c>
+      <c r="O19">
+        <v>2.99829291</v>
+      </c>
+      <c r="P19">
+        <v>6.996016789999999</v>
+      </c>
+      <c r="Q19">
+        <v>11.97601679</v>
+      </c>
+      <c r="R19">
+        <v>0.2048192771084338</v>
+      </c>
+      <c r="S19">
+        <v>0.1594452840129015</v>
+      </c>
+      <c r="T19">
+        <v>0.8552981464370597</v>
+      </c>
+      <c r="U19">
+        <v>0.0447</v>
+      </c>
+      <c r="V19">
+        <v>0.3</v>
+      </c>
+      <c r="W19">
+        <v>0.03129</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y19">
+        <v>45.28329307905567</v>
+      </c>
+      <c r="Z19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>0.18</v>
+      </c>
+      <c r="B20">
+        <v>0.137267234880137</v>
+      </c>
+      <c r="C20">
+        <v>25.10648014751266</v>
+      </c>
+      <c r="D20">
+        <v>30.45248014751266</v>
+      </c>
+      <c r="E20">
+        <v>5.346</v>
+      </c>
+      <c r="F20">
+        <v>5.346</v>
+      </c>
+      <c r="G20">
+        <v>0</v>
+      </c>
+      <c r="H20">
+        <v>29.7</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>15.2</v>
+      </c>
+      <c r="K20">
+        <v>4.98</v>
+      </c>
+      <c r="L20">
+        <v>10.22</v>
+      </c>
+      <c r="M20">
+        <v>0.2389662</v>
+      </c>
+      <c r="N20">
+        <v>9.981033799999999</v>
+      </c>
+      <c r="O20">
+        <v>2.99431014</v>
+      </c>
+      <c r="P20">
+        <v>6.986723659999999</v>
+      </c>
+      <c r="Q20">
+        <v>11.96672366</v>
+      </c>
+      <c r="R20">
+        <v>0.2195121951219512</v>
+      </c>
+      <c r="S20">
+        <v>0.1605305303416305</v>
+      </c>
+      <c r="T20">
+        <v>0.8629918510106279</v>
+      </c>
+      <c r="U20">
+        <v>0.0447</v>
+      </c>
+      <c r="V20">
+        <v>0.3</v>
+      </c>
+      <c r="W20">
+        <v>0.03129</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y20">
+        <v>42.76755457466369</v>
+      </c>
+      <c r="Z20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>0.19</v>
+      </c>
+      <c r="B21">
+        <v>0.1368755840295657</v>
+      </c>
+      <c r="C21">
+        <v>24.85240417713045</v>
+      </c>
+      <c r="D21">
+        <v>30.49540417713045</v>
+      </c>
+      <c r="E21">
+        <v>5.643</v>
+      </c>
+      <c r="F21">
+        <v>5.643</v>
+      </c>
+      <c r="G21">
+        <v>0</v>
+      </c>
+      <c r="H21">
+        <v>29.7</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>15.2</v>
+      </c>
+      <c r="K21">
+        <v>4.98</v>
+      </c>
+      <c r="L21">
+        <v>10.22</v>
+      </c>
+      <c r="M21">
+        <v>0.2522421</v>
+      </c>
+      <c r="N21">
+        <v>9.967757899999999</v>
+      </c>
+      <c r="O21">
+        <v>2.99032737</v>
+      </c>
+      <c r="P21">
+        <v>6.977430529999999</v>
+      </c>
+      <c r="Q21">
+        <v>11.95743053</v>
+      </c>
+      <c r="R21">
+        <v>0.2345679012345679</v>
+      </c>
+      <c r="S21">
+        <v>0.161642572876007</v>
+      </c>
+      <c r="T21">
+        <v>0.8708755235983584</v>
+      </c>
+      <c r="U21">
+        <v>0.0447</v>
+      </c>
+      <c r="V21">
+        <v>0.3</v>
+      </c>
+      <c r="W21">
+        <v>0.03129</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y21">
+        <v>40.51663064968139</v>
+      </c>
+      <c r="Z21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>0.2</v>
+      </c>
+      <c r="B22">
+        <v>0.1364839331789945</v>
+      </c>
+      <c r="C22">
+        <v>24.59844938394078</v>
+      </c>
+      <c r="D22">
+        <v>30.53844938394078</v>
+      </c>
+      <c r="E22">
+        <v>5.94</v>
+      </c>
+      <c r="F22">
+        <v>5.94</v>
+      </c>
+      <c r="G22">
+        <v>0</v>
+      </c>
+      <c r="H22">
+        <v>29.7</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>15.2</v>
+      </c>
+      <c r="K22">
+        <v>4.98</v>
+      </c>
+      <c r="L22">
+        <v>10.22</v>
+      </c>
+      <c r="M22">
+        <v>0.265518</v>
+      </c>
+      <c r="N22">
+        <v>9.954481999999999</v>
+      </c>
+      <c r="O22">
+        <v>2.986344599999999</v>
+      </c>
+      <c r="P22">
+        <v>6.9681374</v>
+      </c>
+      <c r="Q22">
+        <v>11.9481374</v>
+      </c>
+      <c r="R22">
+        <v>0.25</v>
+      </c>
+      <c r="S22">
+        <v>0.1627824164737431</v>
+      </c>
+      <c r="T22">
+        <v>0.8789562880007823</v>
+      </c>
+      <c r="U22">
+        <v>0.0447</v>
+      </c>
+      <c r="V22">
+        <v>0.3</v>
+      </c>
+      <c r="W22">
+        <v>0.03129</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y22">
+        <v>38.49079911719732</v>
+      </c>
+      <c r="Z22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>0.21</v>
+      </c>
+      <c r="B23">
+        <v>0.1360922823284232</v>
+      </c>
+      <c r="C23">
+        <v>24.34461628180509</v>
+      </c>
+      <c r="D23">
+        <v>30.58161628180509</v>
+      </c>
+      <c r="E23">
+        <v>6.236999999999999</v>
+      </c>
+      <c r="F23">
+        <v>6.236999999999999</v>
+      </c>
+      <c r="G23">
+        <v>0</v>
+      </c>
+      <c r="H23">
+        <v>29.7</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>15.2</v>
+      </c>
+      <c r="K23">
+        <v>4.98</v>
+      </c>
+      <c r="L23">
+        <v>10.22</v>
+      </c>
+      <c r="M23">
+        <v>0.2787939</v>
+      </c>
+      <c r="N23">
+        <v>9.941206099999999</v>
+      </c>
+      <c r="O23">
+        <v>2.982361829999999</v>
+      </c>
+      <c r="P23">
+        <v>6.958844269999999</v>
+      </c>
+      <c r="Q23">
+        <v>11.93884427</v>
+      </c>
+      <c r="R23">
+        <v>0.2658227848101266</v>
+      </c>
+      <c r="S23">
+        <v>0.1639511168714217</v>
+      </c>
+      <c r="T23">
+        <v>0.8872416287171914</v>
+      </c>
+      <c r="U23">
+        <v>0.0447</v>
+      </c>
+      <c r="V23">
+        <v>0.3</v>
+      </c>
+      <c r="W23">
+        <v>0.03129</v>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y23">
+        <v>36.65790392114031</v>
+      </c>
+      <c r="Z23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>0.22</v>
+      </c>
+      <c r="B24">
+        <v>0.1357006314778519</v>
+      </c>
+      <c r="C24">
+        <v>24.09090538749429</v>
+      </c>
+      <c r="D24">
+        <v>30.62490538749429</v>
+      </c>
+      <c r="E24">
+        <v>6.534</v>
+      </c>
+      <c r="F24">
+        <v>6.534</v>
+      </c>
+      <c r="G24">
+        <v>0</v>
+      </c>
+      <c r="H24">
+        <v>29.7</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>15.2</v>
+      </c>
+      <c r="K24">
+        <v>4.98</v>
+      </c>
+      <c r="L24">
+        <v>10.22</v>
+      </c>
+      <c r="M24">
+        <v>0.2920698</v>
+      </c>
+      <c r="N24">
+        <v>9.927930199999999</v>
+      </c>
+      <c r="O24">
+        <v>2.97837906</v>
+      </c>
+      <c r="P24">
+        <v>6.949551139999999</v>
+      </c>
+      <c r="Q24">
+        <v>11.92955114</v>
+      </c>
+      <c r="R24">
+        <v>0.282051282051282</v>
+      </c>
+      <c r="S24">
+        <v>0.165149783945964</v>
+      </c>
+      <c r="T24">
+        <v>0.8957394140673547</v>
+      </c>
+      <c r="U24">
+        <v>0.0447</v>
+      </c>
+      <c r="V24">
+        <v>0.3</v>
+      </c>
+      <c r="W24">
+        <v>0.03129</v>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y24">
+        <v>34.99163556108848</v>
+      </c>
+      <c r="Z24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>0.23</v>
+      </c>
+      <c r="B25">
+        <v>0.1353089806272807</v>
+      </c>
+      <c r="C25">
+        <v>23.8373172207095</v>
+      </c>
+      <c r="D25">
+        <v>30.6683172207095</v>
+      </c>
+      <c r="E25">
+        <v>6.831</v>
+      </c>
+      <c r="F25">
+        <v>6.831</v>
+      </c>
+      <c r="G25">
+        <v>0</v>
+      </c>
+      <c r="H25">
+        <v>29.7</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>15.2</v>
+      </c>
+      <c r="K25">
+        <v>4.98</v>
+      </c>
+      <c r="L25">
+        <v>10.22</v>
+      </c>
+      <c r="M25">
+        <v>0.3053457000000001</v>
+      </c>
+      <c r="N25">
+        <v>9.914654299999999</v>
+      </c>
+      <c r="O25">
+        <v>2.97439629</v>
+      </c>
+      <c r="P25">
+        <v>6.940258009999999</v>
+      </c>
+      <c r="Q25">
+        <v>11.92025801</v>
+      </c>
+      <c r="R25">
+        <v>0.2987012987012987</v>
+      </c>
+      <c r="S25">
+        <v>0.1663795852302346</v>
+      </c>
+      <c r="T25">
+        <v>0.9044579211149248</v>
+      </c>
+      <c r="U25">
+        <v>0.0447</v>
+      </c>
+      <c r="V25">
+        <v>0.3</v>
+      </c>
+      <c r="W25">
+        <v>0.03129</v>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y25">
+        <v>33.47026010191071</v>
+      </c>
+      <c r="Z25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <v>0.24</v>
+      </c>
+      <c r="B26">
+        <v>0.1349173297767094</v>
+      </c>
+      <c r="C26">
+        <v>23.58385230410278</v>
+      </c>
+      <c r="D26">
+        <v>30.71185230410278</v>
+      </c>
+      <c r="E26">
+        <v>7.127999999999999</v>
+      </c>
+      <c r="F26">
+        <v>7.127999999999999</v>
+      </c>
+      <c r="G26">
+        <v>0</v>
+      </c>
+      <c r="H26">
+        <v>29.7</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>15.2</v>
+      </c>
+      <c r="K26">
+        <v>4.98</v>
+      </c>
+      <c r="L26">
+        <v>10.22</v>
+      </c>
+      <c r="M26">
+        <v>0.3186216</v>
+      </c>
+      <c r="N26">
+        <v>9.901378399999999</v>
+      </c>
+      <c r="O26">
+        <v>2.97041352</v>
+      </c>
+      <c r="P26">
+        <v>6.930964879999999</v>
+      </c>
+      <c r="Q26">
+        <v>11.91096488</v>
+      </c>
+      <c r="R26">
+        <v>0.3157894736842105</v>
+      </c>
+      <c r="S26">
+        <v>0.1676417497061966</v>
+      </c>
+      <c r="T26">
+        <v>0.9134058625584838</v>
+      </c>
+      <c r="U26">
+        <v>0.0447</v>
+      </c>
+      <c r="V26">
+        <v>0.3</v>
+      </c>
+      <c r="W26">
+        <v>0.03129</v>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y26">
+        <v>32.07566593099777</v>
+      </c>
+      <c r="Z26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <v>0.25</v>
+      </c>
+      <c r="B27">
+        <v>0.1345256789261381</v>
+      </c>
+      <c r="C27">
+        <v>23.33051116329812</v>
+      </c>
+      <c r="D27">
+        <v>30.75551116329812</v>
+      </c>
+      <c r="E27">
+        <v>7.425</v>
+      </c>
+      <c r="F27">
+        <v>7.425</v>
+      </c>
+      <c r="G27">
+        <v>0</v>
+      </c>
+      <c r="H27">
+        <v>29.7</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>15.2</v>
+      </c>
+      <c r="K27">
+        <v>4.98</v>
+      </c>
+      <c r="L27">
+        <v>10.22</v>
+      </c>
+      <c r="M27">
+        <v>0.3318975</v>
+      </c>
+      <c r="N27">
+        <v>9.888102499999999</v>
+      </c>
+      <c r="O27">
+        <v>2.966430749999999</v>
+      </c>
+      <c r="P27">
+        <v>6.92167175</v>
+      </c>
+      <c r="Q27">
+        <v>11.90167175</v>
+      </c>
+      <c r="R27">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="S27">
+        <v>0.1689375719015175</v>
+      </c>
+      <c r="T27">
+        <v>0.9225924157738707</v>
+      </c>
+      <c r="U27">
+        <v>0.0447</v>
+      </c>
+      <c r="V27">
+        <v>0.3</v>
+      </c>
+      <c r="W27">
+        <v>0.03129</v>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y27">
+        <v>30.79263929375786</v>
+      </c>
+      <c r="Z27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28">
+        <v>0.26</v>
+      </c>
+      <c r="B28">
+        <v>0.1341340280755669</v>
+      </c>
+      <c r="C28">
+        <v>23.07729432691261</v>
+      </c>
+      <c r="D28">
+        <v>30.79929432691262</v>
+      </c>
+      <c r="E28">
+        <v>7.722</v>
+      </c>
+      <c r="F28">
+        <v>7.722</v>
+      </c>
+      <c r="G28">
+        <v>0</v>
+      </c>
+      <c r="H28">
+        <v>29.7</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>15.2</v>
+      </c>
+      <c r="K28">
+        <v>4.98</v>
+      </c>
+      <c r="L28">
+        <v>10.22</v>
+      </c>
+      <c r="M28">
+        <v>0.3451734</v>
+      </c>
+      <c r="N28">
+        <v>9.874826599999999</v>
+      </c>
+      <c r="O28">
+        <v>2.962447979999999</v>
+      </c>
+      <c r="P28">
+        <v>6.912378619999999</v>
+      </c>
+      <c r="Q28">
+        <v>11.89237862</v>
+      </c>
+      <c r="R28">
+        <v>0.3513513513513514</v>
+      </c>
+      <c r="S28">
+        <v>0.1702684163183336</v>
+      </c>
+      <c r="T28">
+        <v>0.9320272542112953</v>
+      </c>
+      <c r="U28">
+        <v>0.0447</v>
+      </c>
+      <c r="V28">
+        <v>0.3</v>
+      </c>
+      <c r="W28">
+        <v>0.03129</v>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y28">
+        <v>29.60830701322871</v>
+      </c>
+      <c r="Z28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29">
+        <v>0.27</v>
+      </c>
+      <c r="B29">
+        <v>0.1337423772249956</v>
+      </c>
+      <c r="C29">
+        <v>22.82420232657776</v>
+      </c>
+      <c r="D29">
+        <v>30.84320232657776</v>
+      </c>
+      <c r="E29">
+        <v>8.019</v>
+      </c>
+      <c r="F29">
+        <v>8.019</v>
+      </c>
+      <c r="G29">
+        <v>0</v>
+      </c>
+      <c r="H29">
+        <v>29.7</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>15.2</v>
+      </c>
+      <c r="K29">
+        <v>4.98</v>
+      </c>
+      <c r="L29">
+        <v>10.22</v>
+      </c>
+      <c r="M29">
+        <v>0.3584493</v>
+      </c>
+      <c r="N29">
+        <v>9.861550699999999</v>
+      </c>
+      <c r="O29">
+        <v>2.95846521</v>
+      </c>
+      <c r="P29">
+        <v>6.903085489999999</v>
+      </c>
+      <c r="Q29">
+        <v>11.88308549</v>
+      </c>
+      <c r="R29">
+        <v>0.3698630136986302</v>
+      </c>
+      <c r="S29">
+        <v>0.1716357222260214</v>
+      </c>
+      <c r="T29">
+        <v>0.9417205813730329</v>
+      </c>
+      <c r="U29">
+        <v>0.0447</v>
+      </c>
+      <c r="V29">
+        <v>0.3</v>
+      </c>
+      <c r="W29">
+        <v>0.03129</v>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y29">
+        <v>28.51170304977579</v>
+      </c>
+      <c r="Z29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>0.28</v>
+      </c>
+      <c r="B30">
+        <v>0.1333507263744244</v>
+      </c>
+      <c r="C30">
+        <v>22.571235696961</v>
+      </c>
+      <c r="D30">
+        <v>30.88723569696101</v>
+      </c>
+      <c r="E30">
+        <v>8.316000000000001</v>
+      </c>
+      <c r="F30">
+        <v>8.316000000000001</v>
+      </c>
+      <c r="G30">
+        <v>0</v>
+      </c>
+      <c r="H30">
+        <v>29.7</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>15.2</v>
+      </c>
+      <c r="K30">
+        <v>4.98</v>
+      </c>
+      <c r="L30">
+        <v>10.22</v>
+      </c>
+      <c r="M30">
+        <v>0.3717252000000001</v>
+      </c>
+      <c r="N30">
+        <v>9.848274799999999</v>
+      </c>
+      <c r="O30">
+        <v>2.95448244</v>
+      </c>
+      <c r="P30">
+        <v>6.893792359999999</v>
+      </c>
+      <c r="Q30">
+        <v>11.87379236</v>
+      </c>
+      <c r="R30">
+        <v>0.388888888888889</v>
+      </c>
+      <c r="S30">
+        <v>0.1730410088533672</v>
+      </c>
+      <c r="T30">
+        <v>0.9516831676225963</v>
+      </c>
+      <c r="U30">
+        <v>0.0447</v>
+      </c>
+      <c r="V30">
+        <v>0.3</v>
+      </c>
+      <c r="W30">
+        <v>0.03129</v>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y30">
+        <v>27.49342794085522</v>
+      </c>
+      <c r="Z30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>0.29</v>
+      </c>
+      <c r="B31">
+        <v>0.1329590755238531</v>
+      </c>
+      <c r="C31">
+        <v>22.31839497578743</v>
+      </c>
+      <c r="D31">
+        <v>30.93139497578743</v>
+      </c>
+      <c r="E31">
+        <v>8.613</v>
+      </c>
+      <c r="F31">
+        <v>8.613</v>
+      </c>
+      <c r="G31">
+        <v>0</v>
+      </c>
+      <c r="H31">
+        <v>29.7</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>15.2</v>
+      </c>
+      <c r="K31">
+        <v>4.98</v>
+      </c>
+      <c r="L31">
+        <v>10.22</v>
+      </c>
+      <c r="M31">
+        <v>0.3850011</v>
+      </c>
+      <c r="N31">
+        <v>9.834998899999999</v>
+      </c>
+      <c r="O31">
+        <v>2.95049967</v>
+      </c>
+      <c r="P31">
+        <v>6.884499229999999</v>
+      </c>
+      <c r="Q31">
+        <v>11.86449923</v>
+      </c>
+      <c r="R31">
+        <v>0.4084507042253521</v>
+      </c>
+      <c r="S31">
+        <v>0.1744858810195114</v>
+      </c>
+      <c r="T31">
+        <v>0.9619263901045421</v>
+      </c>
+      <c r="U31">
+        <v>0.0447</v>
+      </c>
+      <c r="V31">
+        <v>0.3</v>
+      </c>
+      <c r="W31">
+        <v>0.03129</v>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y31">
+        <v>26.5453787015154</v>
+      </c>
+      <c r="Z31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <v>0.3</v>
+      </c>
+      <c r="B32">
+        <v>0.1325674246732818</v>
+      </c>
+      <c r="C32">
+        <v>22.06568070386166</v>
+      </c>
+      <c r="D32">
+        <v>30.97568070386166</v>
+      </c>
+      <c r="E32">
+        <v>8.91</v>
+      </c>
+      <c r="F32">
+        <v>8.91</v>
+      </c>
+      <c r="G32">
+        <v>0</v>
+      </c>
+      <c r="H32">
+        <v>29.7</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>15.2</v>
+      </c>
+      <c r="K32">
+        <v>4.98</v>
+      </c>
+      <c r="L32">
+        <v>10.22</v>
+      </c>
+      <c r="M32">
+        <v>0.398277</v>
+      </c>
+      <c r="N32">
+        <v>9.821722999999999</v>
+      </c>
+      <c r="O32">
+        <v>2.946516899999999</v>
+      </c>
+      <c r="P32">
+        <v>6.8752061</v>
+      </c>
+      <c r="Q32">
+        <v>11.8552061</v>
+      </c>
+      <c r="R32">
+        <v>0.4285714285714286</v>
+      </c>
+      <c r="S32">
+        <v>0.1759720352475455</v>
+      </c>
+      <c r="T32">
+        <v>0.9724622760859719</v>
+      </c>
+      <c r="U32">
+        <v>0.0447</v>
+      </c>
+      <c r="V32">
+        <v>0.3</v>
+      </c>
+      <c r="W32">
+        <v>0.03129</v>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y32">
+        <v>25.66053274479821</v>
+      </c>
+      <c r="Z32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
+        <v>0.31</v>
+      </c>
+      <c r="B33">
+        <v>0.1321757738227106</v>
+      </c>
+      <c r="C33">
+        <v>21.8130934250899</v>
+      </c>
+      <c r="D33">
+        <v>31.0200934250899</v>
+      </c>
+      <c r="E33">
+        <v>9.206999999999999</v>
+      </c>
+      <c r="F33">
+        <v>9.206999999999999</v>
+      </c>
+      <c r="G33">
+        <v>0</v>
+      </c>
+      <c r="H33">
+        <v>29.7</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>15.2</v>
+      </c>
+      <c r="K33">
+        <v>4.98</v>
+      </c>
+      <c r="L33">
+        <v>10.22</v>
+      </c>
+      <c r="M33">
+        <v>0.4115529</v>
+      </c>
+      <c r="N33">
+        <v>9.808447099999999</v>
+      </c>
+      <c r="O33">
+        <v>2.942534129999999</v>
+      </c>
+      <c r="P33">
+        <v>6.865912969999999</v>
+      </c>
+      <c r="Q33">
+        <v>11.84591297</v>
+      </c>
+      <c r="R33">
+        <v>0.4492753623188406</v>
+      </c>
+      <c r="S33">
+        <v>0.1775012664097255</v>
+      </c>
+      <c r="T33">
+        <v>0.9833035500668633</v>
+      </c>
+      <c r="U33">
+        <v>0.0447</v>
+      </c>
+      <c r="V33">
+        <v>0.3</v>
+      </c>
+      <c r="W33">
+        <v>0.03129</v>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y33">
+        <v>24.83277362399827</v>
+      </c>
+      <c r="Z33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34">
+        <v>0.32</v>
+      </c>
+      <c r="B34">
+        <v>0.1317841229721393</v>
+      </c>
+      <c r="C34">
+        <v>21.56063368650229</v>
+      </c>
+      <c r="D34">
+        <v>31.06463368650228</v>
+      </c>
+      <c r="E34">
+        <v>9.504</v>
+      </c>
+      <c r="F34">
+        <v>9.504</v>
+      </c>
+      <c r="G34">
+        <v>0</v>
+      </c>
+      <c r="H34">
+        <v>29.7</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>15.2</v>
+      </c>
+      <c r="K34">
+        <v>4.98</v>
+      </c>
+      <c r="L34">
+        <v>10.22</v>
+      </c>
+      <c r="M34">
+        <v>0.4248288</v>
+      </c>
+      <c r="N34">
+        <v>9.795171199999999</v>
+      </c>
+      <c r="O34">
+        <v>2.93855136</v>
+      </c>
+      <c r="P34">
+        <v>6.856619839999999</v>
+      </c>
+      <c r="Q34">
+        <v>11.83661984</v>
+      </c>
+      <c r="R34">
+        <v>0.4705882352941177</v>
+      </c>
+      <c r="S34">
+        <v>0.1790754749590285</v>
+      </c>
+      <c r="T34">
+        <v>0.994463685047193</v>
+      </c>
+      <c r="U34">
+        <v>0.0447</v>
+      </c>
+      <c r="V34">
+        <v>0.3</v>
+      </c>
+      <c r="W34">
+        <v>0.03129</v>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y34">
+        <v>24.05674944824833</v>
+      </c>
+      <c r="Z34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
+        <v>0.33</v>
+      </c>
+      <c r="B35">
+        <v>0.1313924721215681</v>
+      </c>
+      <c r="C35">
+        <v>21.30830203827522</v>
+      </c>
+      <c r="D35">
+        <v>31.10930203827522</v>
+      </c>
+      <c r="E35">
+        <v>9.801</v>
+      </c>
+      <c r="F35">
+        <v>9.801</v>
+      </c>
+      <c r="G35">
+        <v>0</v>
+      </c>
+      <c r="H35">
+        <v>29.7</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>15.2</v>
+      </c>
+      <c r="K35">
+        <v>4.98</v>
+      </c>
+      <c r="L35">
+        <v>10.22</v>
+      </c>
+      <c r="M35">
+        <v>0.4381047000000001</v>
+      </c>
+      <c r="N35">
+        <v>9.781895299999999</v>
+      </c>
+      <c r="O35">
+        <v>2.93456859</v>
+      </c>
+      <c r="P35">
+        <v>6.847326709999999</v>
+      </c>
+      <c r="Q35">
+        <v>11.82732671</v>
+      </c>
+      <c r="R35">
+        <v>0.4925373134328359</v>
+      </c>
+      <c r="S35">
+        <v>0.1806966748083106</v>
+      </c>
+      <c r="T35">
+        <v>1.005956958385144</v>
+      </c>
+      <c r="U35">
+        <v>0.0447</v>
+      </c>
+      <c r="V35">
+        <v>0.3</v>
+      </c>
+      <c r="W35">
+        <v>0.03129</v>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y35">
+        <v>23.32775704072565</v>
+      </c>
+      <c r="Z35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36">
+        <v>0.34</v>
+      </c>
+      <c r="B36">
+        <v>0.1310008212709968</v>
+      </c>
+      <c r="C36">
+        <v>21.05609903375416</v>
+      </c>
+      <c r="D36">
+        <v>31.15409903375416</v>
+      </c>
+      <c r="E36">
+        <v>10.098</v>
+      </c>
+      <c r="F36">
+        <v>10.098</v>
+      </c>
+      <c r="G36">
+        <v>0</v>
+      </c>
+      <c r="H36">
+        <v>29.7</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>15.2</v>
+      </c>
+      <c r="K36">
+        <v>4.98</v>
+      </c>
+      <c r="L36">
+        <v>10.22</v>
+      </c>
+      <c r="M36">
+        <v>0.4513806000000001</v>
+      </c>
+      <c r="N36">
+        <v>9.768619399999999</v>
+      </c>
+      <c r="O36">
+        <v>2.93058582</v>
+      </c>
+      <c r="P36">
+        <v>6.838033579999999</v>
+      </c>
+      <c r="Q36">
+        <v>11.81803358</v>
+      </c>
+      <c r="R36">
+        <v>0.5151515151515152</v>
+      </c>
+      <c r="S36">
+        <v>0.1823670019257528</v>
+      </c>
+      <c r="T36">
+        <v>1.017798512733336</v>
+      </c>
+      <c r="U36">
+        <v>0.0447</v>
+      </c>
+      <c r="V36">
+        <v>0.3</v>
+      </c>
+      <c r="W36">
+        <v>0.03129</v>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y36">
+        <v>22.64164653952783</v>
+      </c>
+      <c r="Z36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37">
+        <v>0.35</v>
+      </c>
+      <c r="B37">
+        <v>0.1306091704204256</v>
+      </c>
+      <c r="C37">
+        <v>20.80402522947633</v>
+      </c>
+      <c r="D37">
+        <v>31.19902522947633</v>
+      </c>
+      <c r="E37">
+        <v>10.395</v>
+      </c>
+      <c r="F37">
+        <v>10.395</v>
+      </c>
+      <c r="G37">
+        <v>0</v>
+      </c>
+      <c r="H37">
+        <v>29.7</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>15.2</v>
+      </c>
+      <c r="K37">
+        <v>4.98</v>
+      </c>
+      <c r="L37">
+        <v>10.22</v>
+      </c>
+      <c r="M37">
+        <v>0.4646565000000001</v>
+      </c>
+      <c r="N37">
+        <v>9.755343499999999</v>
+      </c>
+      <c r="O37">
+        <v>2.926603049999999</v>
+      </c>
+      <c r="P37">
+        <v>6.82874045</v>
+      </c>
+      <c r="Q37">
+        <v>11.80874045</v>
+      </c>
+      <c r="R37">
+        <v>0.5384615384615385</v>
+      </c>
+      <c r="S37">
+        <v>0.1840887237237316</v>
+      </c>
+      <c r="T37">
+        <v>1.030004422599935</v>
+      </c>
+      <c r="U37">
+        <v>0.0447</v>
+      </c>
+      <c r="V37">
+        <v>0.3</v>
+      </c>
+      <c r="W37">
+        <v>0.03129</v>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y37">
+        <v>21.99474235268418</v>
+      </c>
+      <c r="Z37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38">
+        <v>0.36</v>
+      </c>
+      <c r="B38">
+        <v>0.1302175195698543</v>
+      </c>
+      <c r="C38">
+        <v>20.5520811851939</v>
+      </c>
+      <c r="D38">
+        <v>31.2440811851939</v>
+      </c>
+      <c r="E38">
+        <v>10.692</v>
+      </c>
+      <c r="F38">
+        <v>10.692</v>
+      </c>
+      <c r="G38">
+        <v>0</v>
+      </c>
+      <c r="H38">
+        <v>29.7</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <v>15.2</v>
+      </c>
+      <c r="K38">
+        <v>4.98</v>
+      </c>
+      <c r="L38">
+        <v>10.22</v>
+      </c>
+      <c r="M38">
+        <v>0.4779324</v>
+      </c>
+      <c r="N38">
+        <v>9.742067599999999</v>
+      </c>
+      <c r="O38">
+        <v>2.922620279999999</v>
+      </c>
+      <c r="P38">
+        <v>6.819447319999999</v>
+      </c>
+      <c r="Q38">
+        <v>11.79944732</v>
+      </c>
+      <c r="R38">
+        <v>0.5625</v>
+      </c>
+      <c r="S38">
+        <v>0.1858642493278974</v>
+      </c>
+      <c r="T38">
+        <v>1.042591767149864</v>
+      </c>
+      <c r="U38">
+        <v>0.0447</v>
+      </c>
+      <c r="V38">
+        <v>0.3</v>
+      </c>
+      <c r="W38">
+        <v>0.03129</v>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y38">
+        <v>21.38377728733185</v>
+      </c>
+      <c r="Z38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39">
+        <v>0.37</v>
+      </c>
+      <c r="B39">
+        <v>0.129825868719283</v>
+      </c>
+      <c r="C39">
+        <v>20.30026746389714</v>
+      </c>
+      <c r="D39">
+        <v>31.28926746389714</v>
+      </c>
+      <c r="E39">
+        <v>10.989</v>
+      </c>
+      <c r="F39">
+        <v>10.989</v>
+      </c>
+      <c r="G39">
+        <v>0</v>
+      </c>
+      <c r="H39">
+        <v>29.7</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>15.2</v>
+      </c>
+      <c r="K39">
+        <v>4.98</v>
+      </c>
+      <c r="L39">
+        <v>10.22</v>
+      </c>
+      <c r="M39">
+        <v>0.4912083</v>
+      </c>
+      <c r="N39">
+        <v>9.728791699999999</v>
+      </c>
+      <c r="O39">
+        <v>2.918637509999999</v>
+      </c>
+      <c r="P39">
+        <v>6.810154189999999</v>
+      </c>
+      <c r="Q39">
+        <v>11.79015419</v>
+      </c>
+      <c r="R39">
+        <v>0.5873015873015873</v>
+      </c>
+      <c r="S39">
+        <v>0.1876961408242588</v>
+      </c>
+      <c r="T39">
+        <v>1.055578709939474</v>
+      </c>
+      <c r="U39">
+        <v>0.0447</v>
+      </c>
+      <c r="V39">
+        <v>0.3</v>
+      </c>
+      <c r="W39">
+        <v>0.03129</v>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y39">
+        <v>20.8058373606472</v>
+      </c>
+      <c r="Z39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40">
+        <v>0.38</v>
+      </c>
+      <c r="B40">
+        <v>0.1294342178687118</v>
+      </c>
+      <c r="C40">
+        <v>20.04858463183791</v>
+      </c>
+      <c r="D40">
+        <v>31.33458463183791</v>
+      </c>
+      <c r="E40">
+        <v>11.286</v>
+      </c>
+      <c r="F40">
+        <v>11.286</v>
+      </c>
+      <c r="G40">
+        <v>0</v>
+      </c>
+      <c r="H40">
+        <v>29.7</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="J40">
+        <v>15.2</v>
+      </c>
+      <c r="K40">
+        <v>4.98</v>
+      </c>
+      <c r="L40">
+        <v>10.22</v>
+      </c>
+      <c r="M40">
+        <v>0.5044842</v>
+      </c>
+      <c r="N40">
+        <v>9.715515799999999</v>
+      </c>
+      <c r="O40">
+        <v>2.91465474</v>
+      </c>
+      <c r="P40">
+        <v>6.800861059999999</v>
+      </c>
+      <c r="Q40">
+        <v>11.78086106</v>
+      </c>
+      <c r="R40">
+        <v>0.6129032258064516</v>
+      </c>
+      <c r="S40">
+        <v>0.1895871255946964</v>
+      </c>
+      <c r="T40">
+        <v>1.068984586367458</v>
+      </c>
+      <c r="U40">
+        <v>0.0447</v>
+      </c>
+      <c r="V40">
+        <v>0.3</v>
+      </c>
+      <c r="W40">
+        <v>0.03129</v>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y40">
+        <v>20.25831532484069</v>
+      </c>
+      <c r="Z40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41">
+        <v>0.39</v>
+      </c>
+      <c r="B41">
+        <v>0.1290425670181405</v>
+      </c>
+      <c r="C41">
+        <v>19.79703325855331</v>
+      </c>
+      <c r="D41">
+        <v>31.3800332585533</v>
+      </c>
+      <c r="E41">
+        <v>11.583</v>
+      </c>
+      <c r="F41">
+        <v>11.583</v>
+      </c>
+      <c r="G41">
+        <v>0</v>
+      </c>
+      <c r="H41">
+        <v>29.7</v>
+      </c>
+      <c r="I41">
+        <v>0</v>
+      </c>
+      <c r="J41">
+        <v>15.2</v>
+      </c>
+      <c r="K41">
+        <v>4.98</v>
+      </c>
+      <c r="L41">
+        <v>10.22</v>
+      </c>
+      <c r="M41">
+        <v>0.5177601000000001</v>
+      </c>
+      <c r="N41">
+        <v>9.702239899999999</v>
+      </c>
+      <c r="O41">
+        <v>2.91067197</v>
+      </c>
+      <c r="P41">
+        <v>6.791567929999999</v>
+      </c>
+      <c r="Q41">
+        <v>11.77156793</v>
+      </c>
+      <c r="R41">
+        <v>0.639344262295082</v>
+      </c>
+      <c r="S41">
+        <v>0.1915401098658041</v>
+      </c>
+      <c r="T41">
+        <v>1.082829999727507</v>
+      </c>
+      <c r="U41">
+        <v>0.0447</v>
+      </c>
+      <c r="V41">
+        <v>0.3</v>
+      </c>
+      <c r="W41">
+        <v>0.03129</v>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y41">
+        <v>19.73887134215247</v>
+      </c>
+      <c r="Z41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42">
+        <v>0.4</v>
+      </c>
+      <c r="B42">
+        <v>0.1286509161675693</v>
+      </c>
+      <c r="C42">
+        <v>19.54561391688951</v>
+      </c>
+      <c r="D42">
+        <v>31.42561391688951</v>
+      </c>
+      <c r="E42">
+        <v>11.88</v>
+      </c>
+      <c r="F42">
+        <v>11.88</v>
+      </c>
+      <c r="G42">
+        <v>0</v>
+      </c>
+      <c r="H42">
+        <v>29.7</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="J42">
+        <v>15.2</v>
+      </c>
+      <c r="K42">
+        <v>4.98</v>
+      </c>
+      <c r="L42">
+        <v>10.22</v>
+      </c>
+      <c r="M42">
+        <v>0.5310360000000001</v>
+      </c>
+      <c r="N42">
+        <v>9.688963999999999</v>
+      </c>
+      <c r="O42">
+        <v>2.906689199999999</v>
+      </c>
+      <c r="P42">
+        <v>6.7822748</v>
+      </c>
+      <c r="Q42">
+        <v>11.7622748</v>
+      </c>
+      <c r="R42">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="S42">
+        <v>0.1935581936126155</v>
+      </c>
+      <c r="T42">
+        <v>1.097136926866225</v>
+      </c>
+      <c r="U42">
+        <v>0.0447</v>
+      </c>
+      <c r="V42">
+        <v>0.3</v>
+      </c>
+      <c r="W42">
+        <v>0.03129</v>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y42">
+        <v>19.24539955859866</v>
+      </c>
+      <c r="Z42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43">
+        <v>0.41</v>
+      </c>
+      <c r="B43">
+        <v>0.128259265316998</v>
+      </c>
+      <c r="C43">
+        <v>19.29432718302588</v>
+      </c>
+      <c r="D43">
+        <v>31.47132718302588</v>
+      </c>
+      <c r="E43">
+        <v>12.177</v>
+      </c>
+      <c r="F43">
+        <v>12.177</v>
+      </c>
+      <c r="G43">
+        <v>0</v>
+      </c>
+      <c r="H43">
+        <v>29.7</v>
+      </c>
+      <c r="I43">
+        <v>0</v>
+      </c>
+      <c r="J43">
+        <v>15.2</v>
+      </c>
+      <c r="K43">
+        <v>4.98</v>
+      </c>
+      <c r="L43">
+        <v>10.22</v>
+      </c>
+      <c r="M43">
+        <v>0.5443119000000001</v>
+      </c>
+      <c r="N43">
+        <v>9.675688099999999</v>
+      </c>
+      <c r="O43">
+        <v>2.902706429999999</v>
+      </c>
+      <c r="P43">
+        <v>6.772981669999999</v>
+      </c>
+      <c r="Q43">
+        <v>11.75298167</v>
+      </c>
+      <c r="R43">
+        <v>0.6949152542372882</v>
+      </c>
+      <c r="S43">
+        <v>0.1956446869779628</v>
+      </c>
+      <c r="T43">
+        <v>1.111928834585916</v>
+      </c>
+      <c r="U43">
+        <v>0.0447</v>
+      </c>
+      <c r="V43">
+        <v>0.3</v>
+      </c>
+      <c r="W43">
+        <v>0.03129</v>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y43">
+        <v>18.77599956936454</v>
+      </c>
+      <c r="Z43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44">
+        <v>0.42</v>
+      </c>
+      <c r="B44">
+        <v>0.1278676144664267</v>
+      </c>
+      <c r="C44">
+        <v>19.04317363649922</v>
+      </c>
+      <c r="D44">
+        <v>31.51717363649922</v>
+      </c>
+      <c r="E44">
+        <v>12.474</v>
+      </c>
+      <c r="F44">
+        <v>12.474</v>
+      </c>
+      <c r="G44">
+        <v>0</v>
+      </c>
+      <c r="H44">
+        <v>29.7</v>
+      </c>
+      <c r="I44">
+        <v>0</v>
+      </c>
+      <c r="J44">
+        <v>15.2</v>
+      </c>
+      <c r="K44">
+        <v>4.98</v>
+      </c>
+      <c r="L44">
+        <v>10.22</v>
+      </c>
+      <c r="M44">
+        <v>0.5575878</v>
+      </c>
+      <c r="N44">
+        <v>9.662412199999999</v>
+      </c>
+      <c r="O44">
+        <v>2.898723659999999</v>
+      </c>
+      <c r="P44">
+        <v>6.763688539999999</v>
+      </c>
+      <c r="Q44">
+        <v>11.74368854</v>
+      </c>
+      <c r="R44">
+        <v>0.7241379310344827</v>
+      </c>
+      <c r="S44">
+        <v>0.1978031283903909</v>
+      </c>
+      <c r="T44">
+        <v>1.127230808089044</v>
+      </c>
+      <c r="U44">
+        <v>0.0447</v>
+      </c>
+      <c r="V44">
+        <v>0.3</v>
+      </c>
+      <c r="W44">
+        <v>0.03129</v>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y44">
+        <v>18.32895196057015</v>
+      </c>
+      <c r="Z44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45">
+        <v>0.43</v>
+      </c>
+      <c r="B45">
+        <v>0.1274759636158555</v>
+      </c>
+      <c r="C45">
+        <v>18.79215386022823</v>
+      </c>
+      <c r="D45">
+        <v>31.56315386022823</v>
+      </c>
+      <c r="E45">
+        <v>12.771</v>
+      </c>
+      <c r="F45">
+        <v>12.771</v>
+      </c>
+      <c r="G45">
+        <v>0</v>
+      </c>
+      <c r="H45">
+        <v>29.7</v>
+      </c>
+      <c r="I45">
+        <v>0</v>
+      </c>
+      <c r="J45">
+        <v>15.2</v>
+      </c>
+      <c r="K45">
+        <v>4.98</v>
+      </c>
+      <c r="L45">
+        <v>10.22</v>
+      </c>
+      <c r="M45">
+        <v>0.5708637</v>
+      </c>
+      <c r="N45">
+        <v>9.649136299999999</v>
+      </c>
+      <c r="O45">
+        <v>2.89474089</v>
+      </c>
+      <c r="P45">
+        <v>6.754395409999999</v>
+      </c>
+      <c r="Q45">
+        <v>11.73439541</v>
+      </c>
+      <c r="R45">
+        <v>0.7543859649122806</v>
+      </c>
+      <c r="S45">
+        <v>0.2000373045892202</v>
+      </c>
+      <c r="T45">
+        <v>1.14306969294316</v>
+      </c>
+      <c r="U45">
+        <v>0.0447</v>
+      </c>
+      <c r="V45">
+        <v>0.3</v>
+      </c>
+      <c r="W45">
+        <v>0.03129</v>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y45">
+        <v>17.90269726381271</v>
+      </c>
+      <c r="Z45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46">
+        <v>0.44</v>
+      </c>
+      <c r="B46">
+        <v>0.1270843127652842</v>
+      </c>
+      <c r="C46">
+        <v>18.5412684405383</v>
+      </c>
+      <c r="D46">
+        <v>31.6092684405383</v>
+      </c>
+      <c r="E46">
+        <v>13.068</v>
+      </c>
+      <c r="F46">
+        <v>13.068</v>
+      </c>
+      <c r="G46">
+        <v>0</v>
+      </c>
+      <c r="H46">
+        <v>29.7</v>
+      </c>
+      <c r="I46">
+        <v>0</v>
+      </c>
+      <c r="J46">
+        <v>15.2</v>
+      </c>
+      <c r="K46">
+        <v>4.98</v>
+      </c>
+      <c r="L46">
+        <v>10.22</v>
+      </c>
+      <c r="M46">
+        <v>0.5841396</v>
+      </c>
+      <c r="N46">
+        <v>9.635860399999999</v>
+      </c>
+      <c r="O46">
+        <v>2.89075812</v>
+      </c>
+      <c r="P46">
+        <v>6.745102279999999</v>
+      </c>
+      <c r="Q46">
+        <v>11.72510228</v>
+      </c>
+      <c r="R46">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="S46">
+        <v>0.2023512727951504</v>
+      </c>
+      <c r="T46">
+        <v>1.159474252256351</v>
+      </c>
+      <c r="U46">
+        <v>0.0447</v>
+      </c>
+      <c r="V46">
+        <v>0.3</v>
+      </c>
+      <c r="W46">
+        <v>0.03129</v>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y46">
+        <v>17.49581778054424</v>
+      </c>
+      <c r="Z46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47">
+        <v>0.45</v>
+      </c>
+      <c r="B47">
+        <v>0.126692661914713</v>
+      </c>
+      <c r="C47">
+        <v>18.29051796718632</v>
+      </c>
+      <c r="D47">
+        <v>31.65551796718632</v>
+      </c>
+      <c r="E47">
+        <v>13.365</v>
+      </c>
+      <c r="F47">
+        <v>13.365</v>
+      </c>
+      <c r="G47">
+        <v>0</v>
+      </c>
+      <c r="H47">
+        <v>29.7</v>
+      </c>
+      <c r="I47">
+        <v>0</v>
+      </c>
+      <c r="J47">
+        <v>15.2</v>
+      </c>
+      <c r="K47">
+        <v>4.98</v>
+      </c>
+      <c r="L47">
+        <v>10.22</v>
+      </c>
+      <c r="M47">
+        <v>0.5974155000000001</v>
+      </c>
+      <c r="N47">
+        <v>9.622584499999999</v>
+      </c>
+      <c r="O47">
+        <v>2.886775349999999</v>
+      </c>
+      <c r="P47">
+        <v>6.73580915</v>
+      </c>
+      <c r="Q47">
+        <v>11.71580915</v>
+      </c>
+      <c r="R47">
+        <v>0.8181818181818181</v>
+      </c>
+      <c r="S47">
+        <v>0.2047493852994781</v>
+      </c>
+      <c r="T47">
+        <v>1.176475340999113</v>
+      </c>
+      <c r="U47">
+        <v>0.0447</v>
+      </c>
+      <c r="V47">
+        <v>0.3</v>
+      </c>
+      <c r="W47">
+        <v>0.03129</v>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y47">
+        <v>17.10702182986547</v>
+      </c>
+      <c r="Z47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48">
+        <v>0.46</v>
+      </c>
+      <c r="B48">
+        <v>0.1263010110641417</v>
+      </c>
+      <c r="C48">
+        <v>18.03990303338593</v>
+      </c>
+      <c r="D48">
+        <v>31.70190303338594</v>
+      </c>
+      <c r="E48">
+        <v>13.662</v>
+      </c>
+      <c r="F48">
+        <v>13.662</v>
+      </c>
+      <c r="G48">
+        <v>0</v>
+      </c>
+      <c r="H48">
+        <v>29.7</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+      <c r="J48">
+        <v>15.2</v>
+      </c>
+      <c r="K48">
+        <v>4.98</v>
+      </c>
+      <c r="L48">
+        <v>10.22</v>
+      </c>
+      <c r="M48">
+        <v>0.6106914000000001</v>
+      </c>
+      <c r="N48">
+        <v>9.609308599999999</v>
+      </c>
+      <c r="O48">
+        <v>2.882792579999999</v>
+      </c>
+      <c r="P48">
+        <v>6.726516019999999</v>
+      </c>
+      <c r="Q48">
+        <v>11.70651602</v>
+      </c>
+      <c r="R48">
+        <v>0.8518518518518519</v>
+      </c>
+      <c r="S48">
+        <v>0.2072363167854476</v>
+      </c>
+      <c r="T48">
+        <v>1.19410609969531</v>
+      </c>
+      <c r="U48">
+        <v>0.0447</v>
+      </c>
+      <c r="V48">
+        <v>0.3</v>
+      </c>
+      <c r="W48">
+        <v>0.03129</v>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y48">
+        <v>16.73513005095536</v>
+      </c>
+      <c r="Z48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49">
+        <v>0.47</v>
+      </c>
+      <c r="B49">
+        <v>0.1259093602135705</v>
+      </c>
+      <c r="C49">
+        <v>17.78942423583282</v>
+      </c>
+      <c r="D49">
+        <v>31.74842423583282</v>
+      </c>
+      <c r="E49">
+        <v>13.959</v>
+      </c>
+      <c r="F49">
+        <v>13.959</v>
+      </c>
+      <c r="G49">
+        <v>0</v>
+      </c>
+      <c r="H49">
+        <v>29.7</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+      <c r="J49">
+        <v>15.2</v>
+      </c>
+      <c r="K49">
+        <v>4.98</v>
+      </c>
+      <c r="L49">
+        <v>10.22</v>
+      </c>
+      <c r="M49">
+        <v>0.6239673000000001</v>
+      </c>
+      <c r="N49">
+        <v>9.596032699999999</v>
+      </c>
+      <c r="O49">
+        <v>2.878809809999999</v>
+      </c>
+      <c r="P49">
+        <v>6.717222889999999</v>
+      </c>
+      <c r="Q49">
+        <v>11.69722289</v>
+      </c>
+      <c r="R49">
+        <v>0.8867924528301887</v>
+      </c>
+      <c r="S49">
+        <v>0.2098170947425858</v>
+      </c>
+      <c r="T49">
+        <v>1.212402170040421</v>
+      </c>
+      <c r="U49">
+        <v>0.0447</v>
+      </c>
+      <c r="V49">
+        <v>0.3</v>
+      </c>
+      <c r="W49">
+        <v>0.03129</v>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y49">
+        <v>16.37906345412652</v>
+      </c>
+      <c r="Z49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50">
+        <v>0.48</v>
+      </c>
+      <c r="B50">
+        <v>0.1255177093629992</v>
+      </c>
+      <c r="C50">
+        <v>17.53908217473032</v>
+      </c>
+      <c r="D50">
+        <v>31.79508217473032</v>
+      </c>
+      <c r="E50">
+        <v>14.256</v>
+      </c>
+      <c r="F50">
+        <v>14.256</v>
+      </c>
+      <c r="G50">
+        <v>0</v>
+      </c>
+      <c r="H50">
+        <v>29.7</v>
+      </c>
+      <c r="I50">
+        <v>0</v>
+      </c>
+      <c r="J50">
+        <v>15.2</v>
+      </c>
+      <c r="K50">
+        <v>4.98</v>
+      </c>
+      <c r="L50">
+        <v>10.22</v>
+      </c>
+      <c r="M50">
+        <v>0.6372432</v>
+      </c>
+      <c r="N50">
+        <v>9.582756799999999</v>
+      </c>
+      <c r="O50">
+        <v>2.87482704</v>
+      </c>
+      <c r="P50">
+        <v>6.707929759999999</v>
+      </c>
+      <c r="Q50">
+        <v>11.68792976</v>
+      </c>
+      <c r="R50">
+        <v>0.923076923076923</v>
+      </c>
+      <c r="S50">
+        <v>0.2124971333903831</v>
+      </c>
+      <c r="T50">
+        <v>1.231401935398805</v>
+      </c>
+      <c r="U50">
+        <v>0.0447</v>
+      </c>
+      <c r="V50">
+        <v>0.3</v>
+      </c>
+      <c r="W50">
+        <v>0.03129</v>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y50">
+        <v>16.03783296549889</v>
+      </c>
+      <c r="Z50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51">
+        <v>0.49</v>
+      </c>
+      <c r="B51">
+        <v>0.1251260585124279</v>
+      </c>
+      <c r="C51">
+        <v>17.28887745381522</v>
+      </c>
+      <c r="D51">
+        <v>31.84187745381522</v>
+      </c>
+      <c r="E51">
+        <v>14.553</v>
+      </c>
+      <c r="F51">
+        <v>14.553</v>
+      </c>
+      <c r="G51">
+        <v>0</v>
+      </c>
+      <c r="H51">
+        <v>29.7</v>
+      </c>
+      <c r="I51">
+        <v>0</v>
+      </c>
+      <c r="J51">
+        <v>15.2</v>
+      </c>
+      <c r="K51">
+        <v>4.98</v>
+      </c>
+      <c r="L51">
+        <v>10.22</v>
+      </c>
+      <c r="M51">
+        <v>0.6505191</v>
+      </c>
+      <c r="N51">
+        <v>9.569480899999999</v>
+      </c>
+      <c r="O51">
+        <v>2.87084427</v>
+      </c>
+      <c r="P51">
+        <v>6.698636629999999</v>
+      </c>
+      <c r="Q51">
+        <v>11.67863663</v>
+      </c>
+      <c r="R51">
+        <v>0.9607843137254901</v>
+      </c>
+      <c r="S51">
+        <v>0.215282271592996</v>
+      </c>
+      <c r="T51">
+        <v>1.251146789594772</v>
+      </c>
+      <c r="U51">
+        <v>0.0447</v>
+      </c>
+      <c r="V51">
+        <v>0.3</v>
+      </c>
+      <c r="W51">
+        <v>0.03129</v>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y51">
+        <v>15.71053025191727</v>
+      </c>
+      <c r="Z51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52">
+        <v>0.5</v>
+      </c>
+      <c r="B52">
+        <v>0.1247344076618567</v>
+      </c>
+      <c r="C52">
+        <v>17.03881068038383</v>
+      </c>
+      <c r="D52">
+        <v>31.88881068038383</v>
+      </c>
+      <c r="E52">
+        <v>14.85</v>
+      </c>
+      <c r="F52">
+        <v>14.85</v>
+      </c>
+      <c r="G52">
+        <v>0</v>
+      </c>
+      <c r="H52">
+        <v>29.7</v>
+      </c>
+      <c r="I52">
+        <v>0</v>
+      </c>
+      <c r="J52">
+        <v>15.2</v>
+      </c>
+      <c r="K52">
+        <v>4.98</v>
+      </c>
+      <c r="L52">
+        <v>10.22</v>
+      </c>
+      <c r="M52">
+        <v>0.663795</v>
+      </c>
+      <c r="N52">
+        <v>9.556204999999999</v>
+      </c>
+      <c r="O52">
+        <v>2.866861499999999</v>
+      </c>
+      <c r="P52">
+        <v>6.6893435</v>
+      </c>
+      <c r="Q52">
+        <v>11.6693435</v>
+      </c>
+      <c r="R52">
+        <v>1</v>
+      </c>
+      <c r="S52">
+        <v>0.2181788153237134</v>
+      </c>
+      <c r="T52">
+        <v>1.271681437958579</v>
+      </c>
+      <c r="U52">
+        <v>0.0447</v>
+      </c>
+      <c r="V52">
+        <v>0.3</v>
+      </c>
+      <c r="W52">
+        <v>0.03129</v>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y52">
+        <v>15.39631964687893</v>
+      </c>
+      <c r="Z52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53">
+        <v>0.51</v>
+      </c>
+      <c r="B53">
+        <v>0.1243427568112854</v>
+      </c>
+      <c r="C53">
+        <v>16.78888246531822</v>
+      </c>
+      <c r="D53">
+        <v>31.93588246531822</v>
+      </c>
+      <c r="E53">
+        <v>15.147</v>
+      </c>
+      <c r="F53">
+        <v>15.147</v>
+      </c>
+      <c r="G53">
+        <v>0</v>
+      </c>
+      <c r="H53">
+        <v>29.7</v>
+      </c>
+      <c r="I53">
+        <v>0</v>
+      </c>
+      <c r="J53">
+        <v>15.2</v>
+      </c>
+      <c r="K53">
+        <v>4.98</v>
+      </c>
+      <c r="L53">
+        <v>10.22</v>
+      </c>
+      <c r="M53">
+        <v>0.6770709</v>
+      </c>
+      <c r="N53">
+        <v>9.542929099999998</v>
+      </c>
+      <c r="O53">
+        <v>2.862878729999999</v>
+      </c>
+      <c r="P53">
+        <v>6.680050369999999</v>
+      </c>
+      <c r="Q53">
+        <v>11.66005037</v>
+      </c>
+      <c r="R53">
+        <v>1.040816326530612</v>
+      </c>
+      <c r="S53">
+        <v>0.221193585329154</v>
+      </c>
+      <c r="T53">
+        <v>1.293054235235193</v>
+      </c>
+      <c r="U53">
+        <v>0.0447</v>
+      </c>
+      <c r="V53">
+        <v>0.3</v>
+      </c>
+      <c r="W53">
+        <v>0.03129</v>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y53">
+        <v>15.09443102635189</v>
+      </c>
+      <c r="Z53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54">
+        <v>0.52</v>
+      </c>
+      <c r="B54">
+        <v>0.1239511059607142</v>
+      </c>
+      <c r="C54">
+        <v>16.53909342311275</v>
+      </c>
+      <c r="D54">
+        <v>31.98309342311275</v>
+      </c>
+      <c r="E54">
+        <v>15.444</v>
+      </c>
+      <c r="F54">
+        <v>15.444</v>
+      </c>
+      <c r="G54">
+        <v>0</v>
+      </c>
+      <c r="H54">
+        <v>29.7</v>
+      </c>
+      <c r="I54">
+        <v>0</v>
+      </c>
+      <c r="J54">
+        <v>15.2</v>
+      </c>
+      <c r="K54">
+        <v>4.98</v>
+      </c>
+      <c r="L54">
+        <v>10.22</v>
+      </c>
+      <c r="M54">
+        <v>0.6903468</v>
+      </c>
+      <c r="N54">
+        <v>9.529653199999998</v>
+      </c>
+      <c r="O54">
+        <v>2.858895959999999</v>
+      </c>
+      <c r="P54">
+        <v>6.670757239999999</v>
+      </c>
+      <c r="Q54">
+        <v>11.65075724</v>
+      </c>
+      <c r="R54">
+        <v>1.083333333333333</v>
+      </c>
+      <c r="S54">
+        <v>0.2243339707514879</v>
+      </c>
+      <c r="T54">
+        <v>1.315317565731667</v>
+      </c>
+      <c r="U54">
+        <v>0.0447</v>
+      </c>
+      <c r="V54">
+        <v>0.3</v>
+      </c>
+      <c r="W54">
+        <v>0.03129</v>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y54">
+        <v>14.80415350661435</v>
+      </c>
+      <c r="Z54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55">
+        <v>0.53</v>
+      </c>
+      <c r="B55">
+        <v>0.1235594551101429</v>
+      </c>
+      <c r="C55">
+        <v>16.28944417190079</v>
+      </c>
+      <c r="D55">
+        <v>32.03044417190079</v>
+      </c>
+      <c r="E55">
+        <v>15.741</v>
+      </c>
+      <c r="F55">
+        <v>15.741</v>
+      </c>
+      <c r="G55">
+        <v>0</v>
+      </c>
+      <c r="H55">
+        <v>29.7</v>
+      </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
+      <c r="J55">
+        <v>15.2</v>
+      </c>
+      <c r="K55">
+        <v>4.98</v>
+      </c>
+      <c r="L55">
+        <v>10.22</v>
+      </c>
+      <c r="M55">
+        <v>0.7036227</v>
+      </c>
+      <c r="N55">
+        <v>9.516377299999998</v>
+      </c>
+      <c r="O55">
+        <v>2.85491319</v>
+      </c>
+      <c r="P55">
+        <v>6.661464109999999</v>
+      </c>
+      <c r="Q55">
+        <v>11.64146411</v>
+      </c>
+      <c r="R55">
+        <v>1.127659574468085</v>
+      </c>
+      <c r="S55">
+        <v>0.2276079895960487</v>
+      </c>
+      <c r="T55">
+        <v>1.338528271993948</v>
+      </c>
+      <c r="U55">
+        <v>0.0447</v>
+      </c>
+      <c r="V55">
+        <v>0.3</v>
+      </c>
+      <c r="W55">
+        <v>0.03129</v>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y55">
+        <v>14.52482985554616</v>
+      </c>
+      <c r="Z55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56">
+        <v>0.54</v>
+      </c>
+      <c r="B56">
+        <v>0.1231678042595716</v>
+      </c>
+      <c r="C56">
+        <v>16.0399353334817</v>
+      </c>
+      <c r="D56">
+        <v>32.0779353334817</v>
+      </c>
+      <c r="E56">
+        <v>16.038</v>
+      </c>
+      <c r="F56">
+        <v>16.038</v>
+      </c>
+      <c r="G56">
+        <v>0</v>
+      </c>
+      <c r="H56">
+        <v>29.7</v>
+      </c>
+      <c r="I56">
+        <v>0</v>
+      </c>
+      <c r="J56">
+        <v>15.2</v>
+      </c>
+      <c r="K56">
+        <v>4.98</v>
+      </c>
+      <c r="L56">
+        <v>10.22</v>
+      </c>
+      <c r="M56">
+        <v>0.7168986000000001</v>
+      </c>
+      <c r="N56">
+        <v>9.503101399999998</v>
+      </c>
+      <c r="O56">
+        <v>2.85093042</v>
+      </c>
+      <c r="P56">
+        <v>6.652170979999999</v>
+      </c>
+      <c r="Q56">
+        <v>11.63217098</v>
+      </c>
+      <c r="R56">
+        <v>1.173913043478261</v>
+      </c>
+      <c r="S56">
+        <v>0.2310243570860253</v>
+      </c>
+      <c r="T56">
+        <v>1.362748139398068</v>
+      </c>
+      <c r="U56">
+        <v>0.0447</v>
+      </c>
+      <c r="V56">
+        <v>0.3</v>
+      </c>
+      <c r="W56">
+        <v>0.03129</v>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y56">
+        <v>14.2558515248879</v>
+      </c>
+      <c r="Z56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57">
+        <v>0.55</v>
+      </c>
+      <c r="B57">
+        <v>0.1227761534090004</v>
+      </c>
+      <c r="C57">
+        <v>15.79056753334808</v>
+      </c>
+      <c r="D57">
+        <v>32.12556753334808</v>
+      </c>
+      <c r="E57">
+        <v>16.335</v>
+      </c>
+      <c r="F57">
+        <v>16.335</v>
+      </c>
+      <c r="G57">
+        <v>0</v>
+      </c>
+      <c r="H57">
+        <v>29.7</v>
+      </c>
+      <c r="I57">
+        <v>0</v>
+      </c>
+      <c r="J57">
+        <v>15.2</v>
+      </c>
+      <c r="K57">
+        <v>4.98</v>
+      </c>
+      <c r="L57">
+        <v>10.22</v>
+      </c>
+      <c r="M57">
+        <v>0.7301745000000001</v>
+      </c>
+      <c r="N57">
+        <v>9.489825499999998</v>
+      </c>
+      <c r="O57">
+        <v>2.846947649999999</v>
+      </c>
+      <c r="P57">
+        <v>6.64287785</v>
+      </c>
+      <c r="Q57">
+        <v>11.62287785</v>
+      </c>
+      <c r="R57">
+        <v>1.222222222222223</v>
+      </c>
+      <c r="S57">
+        <v>0.234592563131112</v>
+      </c>
+      <c r="T57">
+        <v>1.388044445353481</v>
+      </c>
+      <c r="U57">
+        <v>0.0447</v>
+      </c>
+      <c r="V57">
+        <v>0.3</v>
+      </c>
+      <c r="W57">
+        <v>0.03129</v>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y57">
+        <v>13.99665422443539</v>
+      </c>
+      <c r="Z57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="B58">
+        <v>0.1223845025584291</v>
+      </c>
+      <c r="C58">
+        <v>15.54134140071319</v>
+      </c>
+      <c r="D58">
+        <v>32.17334140071319</v>
+      </c>
+      <c r="E58">
+        <v>16.632</v>
+      </c>
+      <c r="F58">
+        <v>16.632</v>
+      </c>
+      <c r="G58">
+        <v>0</v>
+      </c>
+      <c r="H58">
+        <v>29.7</v>
+      </c>
+      <c r="I58">
+        <v>0</v>
+      </c>
+      <c r="J58">
+        <v>15.2</v>
+      </c>
+      <c r="K58">
+        <v>4.98</v>
+      </c>
+      <c r="L58">
+        <v>10.22</v>
+      </c>
+      <c r="M58">
+        <v>0.7434504000000002</v>
+      </c>
+      <c r="N58">
+        <v>9.476549599999998</v>
+      </c>
+      <c r="O58">
+        <v>2.842964879999999</v>
+      </c>
+      <c r="P58">
+        <v>6.633584719999999</v>
+      </c>
+      <c r="Q58">
+        <v>11.61358472</v>
+      </c>
+      <c r="R58">
+        <v>1.272727272727273</v>
+      </c>
+      <c r="S58">
+        <v>0.2383229603600662</v>
+      </c>
+      <c r="T58">
+        <v>1.414490583397777</v>
+      </c>
+      <c r="U58">
+        <v>0.0447</v>
+      </c>
+      <c r="V58">
+        <v>0.3</v>
+      </c>
+      <c r="W58">
+        <v>0.03129</v>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y58">
+        <v>13.74671397042761</v>
+      </c>
+      <c r="Z58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59">
+        <v>0.5700000000000001</v>
+      </c>
+      <c r="B59">
+        <v>0.1219928517078579</v>
+      </c>
+      <c r="C59">
+        <v>15.29225756853864</v>
+      </c>
+      <c r="D59">
+        <v>32.22125756853865</v>
+      </c>
+      <c r="E59">
+        <v>16.929</v>
+      </c>
+      <c r="F59">
+        <v>16.929</v>
+      </c>
+      <c r="G59">
+        <v>0</v>
+      </c>
+      <c r="H59">
+        <v>29.7</v>
+      </c>
+      <c r="I59">
+        <v>0</v>
+      </c>
+      <c r="J59">
+        <v>15.2</v>
+      </c>
+      <c r="K59">
+        <v>4.98</v>
+      </c>
+      <c r="L59">
+        <v>10.22</v>
+      </c>
+      <c r="M59">
+        <v>0.7567263000000002</v>
+      </c>
+      <c r="N59">
+        <v>9.463273699999998</v>
+      </c>
+      <c r="O59">
+        <v>2.838982109999999</v>
+      </c>
+      <c r="P59">
+        <v>6.624291589999999</v>
+      </c>
+      <c r="Q59">
+        <v>11.60429159</v>
+      </c>
+      <c r="R59">
+        <v>1.325581395348838</v>
+      </c>
+      <c r="S59">
+        <v>0.2422268644368788</v>
+      </c>
+      <c r="T59">
+        <v>1.442166774374366</v>
+      </c>
+      <c r="U59">
+        <v>0.0447</v>
+      </c>
+      <c r="V59">
+        <v>0.3</v>
+      </c>
+      <c r="W59">
+        <v>0.03129</v>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y59">
+        <v>13.50554354989379</v>
+      </c>
+      <c r="Z59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60">
+        <v>0.58</v>
+      </c>
+      <c r="B60">
+        <v>0.1216012008572866</v>
+      </c>
+      <c r="C60">
+        <v>15.04331667356245</v>
+      </c>
+      <c r="D60">
+        <v>32.26931667356245</v>
+      </c>
+      <c r="E60">
+        <v>17.226</v>
+      </c>
+      <c r="F60">
+        <v>17.226</v>
+      </c>
+      <c r="G60">
+        <v>0</v>
+      </c>
+      <c r="H60">
+        <v>29.7</v>
+      </c>
+      <c r="I60">
+        <v>0</v>
+      </c>
+      <c r="J60">
+        <v>15.2</v>
+      </c>
+      <c r="K60">
+        <v>4.98</v>
+      </c>
+      <c r="L60">
+        <v>10.22</v>
+      </c>
+      <c r="M60">
+        <v>0.7700022</v>
+      </c>
+      <c r="N60">
+        <v>9.449997799999998</v>
+      </c>
+      <c r="O60">
+        <v>2.83499934</v>
+      </c>
+      <c r="P60">
+        <v>6.614998459999999</v>
+      </c>
+      <c r="Q60">
+        <v>11.59499846</v>
+      </c>
+      <c r="R60">
+        <v>1.380952380952381</v>
+      </c>
+      <c r="S60">
+        <v>0.2463166687078252</v>
+      </c>
+      <c r="T60">
+        <v>1.471160879206983</v>
+      </c>
+      <c r="U60">
+        <v>0.0447</v>
+      </c>
+      <c r="V60">
+        <v>0.3</v>
+      </c>
+      <c r="W60">
+        <v>0.03129</v>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y60">
+        <v>13.2726893507577</v>
+      </c>
+      <c r="Z60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61">
+        <v>0.59</v>
+      </c>
+      <c r="B61">
+        <v>0.1212095500067153</v>
+      </c>
+      <c r="C61">
+        <v>14.7945193563271</v>
+      </c>
+      <c r="D61">
+        <v>32.3175193563271</v>
+      </c>
+      <c r="E61">
+        <v>17.523</v>
+      </c>
+      <c r="F61">
+        <v>17.523</v>
+      </c>
+      <c r="G61">
+        <v>0</v>
+      </c>
+      <c r="H61">
+        <v>29.7</v>
+      </c>
+      <c r="I61">
+        <v>0</v>
+      </c>
+      <c r="J61">
+        <v>15.2</v>
+      </c>
+      <c r="K61">
+        <v>4.98</v>
+      </c>
+      <c r="L61">
+        <v>10.22</v>
+      </c>
+      <c r="M61">
+        <v>0.7832781000000001</v>
+      </c>
+      <c r="N61">
+        <v>9.436721899999998</v>
+      </c>
+      <c r="O61">
+        <v>2.83101657</v>
+      </c>
+      <c r="P61">
+        <v>6.605705329999999</v>
+      </c>
+      <c r="Q61">
+        <v>11.58570533</v>
+      </c>
+      <c r="R61">
+        <v>1.439024390243902</v>
+      </c>
+      <c r="S61">
+        <v>0.250605975626135</v>
+      </c>
+      <c r="T61">
+        <v>1.501569330616801</v>
+      </c>
+      <c r="U61">
+        <v>0.0447</v>
+      </c>
+      <c r="V61">
+        <v>0.3</v>
+      </c>
+      <c r="W61">
+        <v>0.03129</v>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y61">
+        <v>13.04772851430418</v>
+      </c>
+      <c r="Z61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62">
+        <v>0.6</v>
+      </c>
+      <c r="B62">
+        <v>0.1208178991561441</v>
+      </c>
+      <c r="C62">
+        <v>14.54586626120812</v>
+      </c>
+      <c r="D62">
+        <v>32.36586626120812</v>
+      </c>
+      <c r="E62">
+        <v>17.82</v>
+      </c>
+      <c r="F62">
+        <v>17.82</v>
+      </c>
+      <c r="G62">
+        <v>0</v>
+      </c>
+      <c r="H62">
+        <v>29.7</v>
+      </c>
+      <c r="I62">
+        <v>0</v>
+      </c>
+      <c r="J62">
+        <v>15.2</v>
+      </c>
+      <c r="K62">
+        <v>4.98</v>
+      </c>
+      <c r="L62">
+        <v>10.22</v>
+      </c>
+      <c r="M62">
+        <v>0.7965540000000001</v>
+      </c>
+      <c r="N62">
+        <v>9.423445999999998</v>
+      </c>
+      <c r="O62">
+        <v>2.827033799999999</v>
+      </c>
+      <c r="P62">
+        <v>6.5964122</v>
+      </c>
+      <c r="Q62">
+        <v>11.5764122</v>
+      </c>
+      <c r="R62">
+        <v>1.5</v>
+      </c>
+      <c r="S62">
+        <v>0.2551097478903602</v>
+      </c>
+      <c r="T62">
+        <v>1.533498204597109</v>
+      </c>
+      <c r="U62">
+        <v>0.0447</v>
+      </c>
+      <c r="V62">
+        <v>0.3</v>
+      </c>
+      <c r="W62">
+        <v>0.03129</v>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y62">
+        <v>12.83026637239911</v>
+      </c>
+      <c r="Z62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63">
+        <v>0.61</v>
+      </c>
+      <c r="B63">
+        <v>0.1208959483055728</v>
+      </c>
+      <c r="C63">
+        <v>14.23922003284337</v>
+      </c>
+      <c r="D63">
+        <v>32.35622003284337</v>
+      </c>
+      <c r="E63">
+        <v>18.117</v>
+      </c>
+      <c r="F63">
+        <v>18.117</v>
+      </c>
+      <c r="G63">
+        <v>0</v>
+      </c>
+      <c r="H63">
+        <v>29.7</v>
+      </c>
+      <c r="I63">
+        <v>0</v>
+      </c>
+      <c r="J63">
+        <v>15.2</v>
+      </c>
+      <c r="K63">
+        <v>4.98</v>
+      </c>
+      <c r="L63">
+        <v>10.22</v>
+      </c>
+      <c r="M63">
+        <v>0.8297586</v>
+      </c>
+      <c r="N63">
+        <v>9.390241399999999</v>
+      </c>
+      <c r="O63">
+        <v>2.81707242</v>
+      </c>
+      <c r="P63">
+        <v>6.573168979999999</v>
+      </c>
+      <c r="Q63">
+        <v>11.55316898</v>
+      </c>
+      <c r="R63">
+        <v>1.564102564102564</v>
+      </c>
+      <c r="S63">
+        <v>0.2598444828348021</v>
+      </c>
+      <c r="T63">
+        <v>1.567064456730254</v>
+      </c>
+      <c r="U63">
+        <v>0.0458</v>
+      </c>
+      <c r="V63">
+        <v>0.3</v>
+      </c>
+      <c r="W63">
+        <v>0.03206</v>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y63">
+        <v>12.31683528197237</v>
+      </c>
+      <c r="Z63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64">
+        <v>0.62</v>
+      </c>
+      <c r="B64">
+        <v>0.1205119974550016</v>
+      </c>
+      <c r="C64">
+        <v>13.98972868951054</v>
+      </c>
+      <c r="D64">
+        <v>32.40372868951054</v>
+      </c>
+      <c r="E64">
+        <v>18.414</v>
+      </c>
+      <c r="F64">
+        <v>18.414</v>
+      </c>
+      <c r="G64">
+        <v>0</v>
+      </c>
+      <c r="H64">
+        <v>29.7</v>
+      </c>
+      <c r="I64">
+        <v>0</v>
+      </c>
+      <c r="J64">
+        <v>15.2</v>
+      </c>
+      <c r="K64">
+        <v>4.98</v>
+      </c>
+      <c r="L64">
+        <v>10.22</v>
+      </c>
+      <c r="M64">
+        <v>0.8433611999999999</v>
+      </c>
+      <c r="N64">
+        <v>9.376638799999998</v>
+      </c>
+      <c r="O64">
+        <v>2.812991639999999</v>
+      </c>
+      <c r="P64">
+        <v>6.563647159999999</v>
+      </c>
+      <c r="Q64">
+        <v>11.54364716</v>
+      </c>
+      <c r="R64">
+        <v>1.631578947368421</v>
+      </c>
+      <c r="S64">
+        <v>0.2648284143552673</v>
+      </c>
+      <c r="T64">
+        <v>1.602397353712512</v>
+      </c>
+      <c r="U64">
+        <v>0.0458</v>
+      </c>
+      <c r="V64">
+        <v>0.3</v>
+      </c>
+      <c r="W64">
+        <v>0.03206</v>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y64">
+        <v>12.11817664839217</v>
+      </c>
+      <c r="Z64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65">
+        <v>0.63</v>
+      </c>
+      <c r="B65">
+        <v>0.1201280466044303</v>
+      </c>
+      <c r="C65">
+        <v>13.74037706530373</v>
+      </c>
+      <c r="D65">
+        <v>32.45137706530373</v>
+      </c>
+      <c r="E65">
+        <v>18.711</v>
+      </c>
+      <c r="F65">
+        <v>18.711</v>
+      </c>
+      <c r="G65">
+        <v>0</v>
+      </c>
+      <c r="H65">
+        <v>29.7</v>
+      </c>
+      <c r="I65">
+        <v>0</v>
+      </c>
+      <c r="J65">
+        <v>15.2</v>
+      </c>
+      <c r="K65">
+        <v>4.98</v>
+      </c>
+      <c r="L65">
+        <v>10.22</v>
+      </c>
+      <c r="M65">
+        <v>0.8569637999999999</v>
+      </c>
+      <c r="N65">
+        <v>9.3630362</v>
+      </c>
+      <c r="O65">
+        <v>2.80891086</v>
+      </c>
+      <c r="P65">
+        <v>6.554125340000001</v>
+      </c>
+      <c r="Q65">
+        <v>11.53412534</v>
+      </c>
+      <c r="R65">
+        <v>1.702702702702703</v>
+      </c>
+      <c r="S65">
+        <v>0.2700817475795414</v>
+      </c>
+      <c r="T65">
+        <v>1.639640137018135</v>
+      </c>
+      <c r="U65">
+        <v>0.0458</v>
+      </c>
+      <c r="V65">
+        <v>0.3</v>
+      </c>
+      <c r="W65">
+        <v>0.03206</v>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y65">
+        <v>11.92582463810023</v>
+      </c>
+      <c r="Z65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66">
+        <v>0.64</v>
+      </c>
+      <c r="B66">
+        <v>0.1197440957538591</v>
+      </c>
+      <c r="C66">
+        <v>13.49116577748463</v>
+      </c>
+      <c r="D66">
+        <v>32.49916577748463</v>
+      </c>
+      <c r="E66">
+        <v>19.008</v>
+      </c>
+      <c r="F66">
+        <v>19.008</v>
+      </c>
+      <c r="G66">
+        <v>0</v>
+      </c>
+      <c r="H66">
+        <v>29.7</v>
+      </c>
+      <c r="I66">
+        <v>0</v>
+      </c>
+      <c r="J66">
+        <v>15.2</v>
+      </c>
+      <c r="K66">
+        <v>4.98</v>
+      </c>
+      <c r="L66">
+        <v>10.22</v>
+      </c>
+      <c r="M66">
+        <v>0.8705664</v>
+      </c>
+      <c r="N66">
+        <v>9.349433599999999</v>
+      </c>
+      <c r="O66">
+        <v>2.80483008</v>
+      </c>
+      <c r="P66">
+        <v>6.544603519999999</v>
+      </c>
+      <c r="Q66">
+        <v>11.52460352</v>
+      </c>
+      <c r="R66">
+        <v>1.777777777777778</v>
+      </c>
+      <c r="S66">
+        <v>0.2756269326496085</v>
+      </c>
+      <c r="T66">
+        <v>1.678951963840738</v>
+      </c>
+      <c r="U66">
+        <v>0.0458</v>
+      </c>
+      <c r="V66">
+        <v>0.3</v>
+      </c>
+      <c r="W66">
+        <v>0.03206</v>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y66">
+        <v>11.73948362812992</v>
+      </c>
+      <c r="Z66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67">
+        <v>0.65</v>
+      </c>
+      <c r="B67">
+        <v>0.1193601449032878</v>
+      </c>
+      <c r="C67">
+        <v>13.24209544695625</v>
+      </c>
+      <c r="D67">
+        <v>32.54709544695625</v>
+      </c>
+      <c r="E67">
+        <v>19.305</v>
+      </c>
+      <c r="F67">
+        <v>19.305</v>
+      </c>
+      <c r="G67">
+        <v>0</v>
+      </c>
+      <c r="H67">
+        <v>29.7</v>
+      </c>
+      <c r="I67">
+        <v>0</v>
+      </c>
+      <c r="J67">
+        <v>15.2</v>
+      </c>
+      <c r="K67">
+        <v>4.98</v>
+      </c>
+      <c r="L67">
+        <v>10.22</v>
+      </c>
+      <c r="M67">
+        <v>0.884169</v>
+      </c>
+      <c r="N67">
+        <v>9.335830999999999</v>
+      </c>
+      <c r="O67">
+        <v>2.8007493</v>
+      </c>
+      <c r="P67">
+        <v>6.535081699999999</v>
+      </c>
+      <c r="Q67">
+        <v>11.5150817</v>
+      </c>
+      <c r="R67">
+        <v>1.857142857142857</v>
+      </c>
+      <c r="S67">
+        <v>0.2814889854379651</v>
+      </c>
+      <c r="T67">
+        <v>1.720510180767489</v>
+      </c>
+      <c r="U67">
+        <v>0.0458</v>
+      </c>
+      <c r="V67">
+        <v>0.3</v>
+      </c>
+      <c r="W67">
+        <v>0.03206</v>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y67">
+        <v>11.55887618769715</v>
+      </c>
+      <c r="Z67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68">
+        <v>0.66</v>
+      </c>
+      <c r="B68">
+        <v>0.1189761940527165</v>
+      </c>
+      <c r="C68">
+        <v>12.99316669828983</v>
+      </c>
+      <c r="D68">
+        <v>32.59516669828983</v>
+      </c>
+      <c r="E68">
+        <v>19.602</v>
+      </c>
+      <c r="F68">
+        <v>19.602</v>
+      </c>
+      <c r="G68">
+        <v>0</v>
+      </c>
+      <c r="H68">
+        <v>29.7</v>
+      </c>
+      <c r="I68">
+        <v>0</v>
+      </c>
+      <c r="J68">
+        <v>15.2</v>
+      </c>
+      <c r="K68">
+        <v>4.98</v>
+      </c>
+      <c r="L68">
+        <v>10.22</v>
+      </c>
+      <c r="M68">
+        <v>0.8977716</v>
+      </c>
+      <c r="N68">
+        <v>9.322228399999998</v>
+      </c>
+      <c r="O68">
+        <v>2.796668519999999</v>
+      </c>
+      <c r="P68">
+        <v>6.525559879999999</v>
+      </c>
+      <c r="Q68">
+        <v>11.50555988</v>
+      </c>
+      <c r="R68">
+        <v>1.941176470588236</v>
+      </c>
+      <c r="S68">
+        <v>0.287695864860931</v>
+      </c>
+      <c r="T68">
+        <v>1.764512998689931</v>
+      </c>
+      <c r="U68">
+        <v>0.0458</v>
+      </c>
+      <c r="V68">
+        <v>0.3</v>
+      </c>
+      <c r="W68">
+        <v>0.03206</v>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y68">
+        <v>11.38374170000477</v>
+      </c>
+      <c r="Z68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69">
+        <v>0.67</v>
+      </c>
+      <c r="B69">
+        <v>0.1185922432021453</v>
+      </c>
+      <c r="C69">
+        <v>12.74438015975199</v>
+      </c>
+      <c r="D69">
+        <v>32.64338015975199</v>
+      </c>
+      <c r="E69">
+        <v>19.899</v>
+      </c>
+      <c r="F69">
+        <v>19.899</v>
+      </c>
+      <c r="G69">
+        <v>0</v>
+      </c>
+      <c r="H69">
+        <v>29.7</v>
+      </c>
+      <c r="I69">
+        <v>0</v>
+      </c>
+      <c r="J69">
+        <v>15.2</v>
+      </c>
+      <c r="K69">
+        <v>4.98</v>
+      </c>
+      <c r="L69">
+        <v>10.22</v>
+      </c>
+      <c r="M69">
+        <v>0.9113742</v>
+      </c>
+      <c r="N69">
+        <v>9.308625799999998</v>
+      </c>
+      <c r="O69">
+        <v>2.792587739999999</v>
+      </c>
+      <c r="P69">
+        <v>6.516038059999999</v>
+      </c>
+      <c r="Q69">
+        <v>11.49603806</v>
+      </c>
+      <c r="R69">
+        <v>2.030303030303031</v>
+      </c>
+      <c r="S69">
+        <v>0.2942789187943797</v>
+      </c>
+      <c r="T69">
+        <v>1.811182654062218</v>
+      </c>
+      <c r="U69">
+        <v>0.0458</v>
+      </c>
+      <c r="V69">
+        <v>0.3</v>
+      </c>
+      <c r="W69">
+        <v>0.03206</v>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y69">
+        <v>11.21383510746738</v>
+      </c>
+      <c r="Z69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70">
+        <v>0.68</v>
+      </c>
+      <c r="B70">
+        <v>0.118208292351574</v>
+      </c>
+      <c r="C70">
+        <v>12.49573646333207</v>
+      </c>
+      <c r="D70">
+        <v>32.69173646333207</v>
+      </c>
+      <c r="E70">
+        <v>20.196</v>
+      </c>
+      <c r="F70">
+        <v>20.196</v>
+      </c>
+      <c r="G70">
+        <v>0</v>
+      </c>
+      <c r="H70">
+        <v>29.7</v>
+      </c>
+      <c r="I70">
+        <v>0</v>
+      </c>
+      <c r="J70">
+        <v>15.2</v>
+      </c>
+      <c r="K70">
+        <v>4.98</v>
+      </c>
+      <c r="L70">
+        <v>10.22</v>
+      </c>
+      <c r="M70">
+        <v>0.9249768</v>
+      </c>
+      <c r="N70">
+        <v>9.295023199999999</v>
+      </c>
+      <c r="O70">
+        <v>2.78850696</v>
+      </c>
+      <c r="P70">
+        <v>6.50651624</v>
+      </c>
+      <c r="Q70">
+        <v>11.48651624</v>
+      </c>
+      <c r="R70">
+        <v>2.125</v>
+      </c>
+      <c r="S70">
+        <v>0.3012734135986689</v>
+      </c>
+      <c r="T70">
+        <v>1.860769162895273</v>
+      </c>
+      <c r="U70">
+        <v>0.0458</v>
+      </c>
+      <c r="V70">
+        <v>0.3</v>
+      </c>
+      <c r="W70">
+        <v>0.03206</v>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y70">
+        <v>11.04892576765168</v>
+      </c>
+      <c r="Z70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71">
+        <v>0.6900000000000001</v>
+      </c>
+      <c r="B71">
+        <v>0.1178243415010028</v>
+      </c>
+      <c r="C71">
+        <v>12.24723624476977</v>
+      </c>
+      <c r="D71">
+        <v>32.74023624476978</v>
+      </c>
+      <c r="E71">
+        <v>20.493</v>
+      </c>
+      <c r="F71">
+        <v>20.493</v>
+      </c>
+      <c r="G71">
+        <v>0</v>
+      </c>
+      <c r="H71">
+        <v>29.7</v>
+      </c>
+      <c r="I71">
+        <v>0</v>
+      </c>
+      <c r="J71">
+        <v>15.2</v>
+      </c>
+      <c r="K71">
+        <v>4.98</v>
+      </c>
+      <c r="L71">
+        <v>10.22</v>
+      </c>
+      <c r="M71">
+        <v>0.9385794000000001</v>
+      </c>
+      <c r="N71">
+        <v>9.281420599999999</v>
+      </c>
+      <c r="O71">
+        <v>2.78442618</v>
+      </c>
+      <c r="P71">
+        <v>6.496994419999999</v>
+      </c>
+      <c r="Q71">
+        <v>11.47699442</v>
+      </c>
+      <c r="R71">
+        <v>2.225806451612904</v>
+      </c>
+      <c r="S71">
+        <v>0.308719166132267</v>
+      </c>
+      <c r="T71">
+        <v>1.913554801330461</v>
+      </c>
+      <c r="U71">
+        <v>0.0458</v>
+      </c>
+      <c r="V71">
+        <v>0.3</v>
+      </c>
+      <c r="W71">
+        <v>0.03206</v>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y71">
+        <v>10.88879640870021</v>
+      </c>
+      <c r="Z71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72">
+        <v>0.7000000000000001</v>
+      </c>
+      <c r="B72">
+        <v>0.1174403906504315</v>
+      </c>
+      <c r="C72">
+        <v>11.998880143583</v>
+      </c>
+      <c r="D72">
+        <v>32.788880143583</v>
+      </c>
+      <c r="E72">
+        <v>20.79</v>
+      </c>
+      <c r="F72">
+        <v>20.79</v>
+      </c>
+      <c r="G72">
+        <v>0</v>
+      </c>
+      <c r="H72">
+        <v>29.7</v>
+      </c>
+      <c r="I72">
+        <v>0</v>
+      </c>
+      <c r="J72">
+        <v>15.2</v>
+      </c>
+      <c r="K72">
+        <v>4.98</v>
+      </c>
+      <c r="L72">
+        <v>10.22</v>
+      </c>
+      <c r="M72">
+        <v>0.9521820000000001</v>
+      </c>
+      <c r="N72">
+        <v>9.267817999999998</v>
+      </c>
+      <c r="O72">
+        <v>2.780345399999999</v>
+      </c>
+      <c r="P72">
+        <v>6.487472599999998</v>
+      </c>
+      <c r="Q72">
+        <v>11.4674726</v>
+      </c>
+      <c r="R72">
+        <v>2.333333333333334</v>
+      </c>
+      <c r="S72">
+        <v>0.3166613021681051</v>
+      </c>
+      <c r="T72">
+        <v>1.969859482327995</v>
+      </c>
+      <c r="U72">
+        <v>0.0458</v>
+      </c>
+      <c r="V72">
+        <v>0.3</v>
+      </c>
+      <c r="W72">
+        <v>0.03206</v>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y72">
+        <v>10.73324217429021</v>
+      </c>
+      <c r="Z72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73">
+        <v>0.71</v>
+      </c>
+      <c r="B73">
+        <v>0.1170564397998603</v>
+      </c>
+      <c r="C73">
+        <v>11.75066880309596</v>
+      </c>
+      <c r="D73">
+        <v>32.83766880309596</v>
+      </c>
+      <c r="E73">
+        <v>21.087</v>
+      </c>
+      <c r="F73">
+        <v>21.087</v>
+      </c>
+      <c r="G73">
+        <v>0</v>
+      </c>
+      <c r="H73">
+        <v>29.7</v>
+      </c>
+      <c r="I73">
+        <v>0</v>
+      </c>
+      <c r="J73">
+        <v>15.2</v>
+      </c>
+      <c r="K73">
+        <v>4.98</v>
+      </c>
+      <c r="L73">
+        <v>10.22</v>
+      </c>
+      <c r="M73">
+        <v>0.9657846</v>
+      </c>
+      <c r="N73">
+        <v>9.2542154</v>
+      </c>
+      <c r="O73">
+        <v>2.77626462</v>
+      </c>
+      <c r="P73">
+        <v>6.47795078</v>
+      </c>
+      <c r="Q73">
+        <v>11.45795078</v>
+      </c>
+      <c r="R73">
+        <v>2.448275862068965</v>
+      </c>
+      <c r="S73">
+        <v>0.325151171723656</v>
+      </c>
+      <c r="T73">
+        <v>2.030047244773634</v>
+      </c>
+      <c r="U73">
+        <v>0.0458</v>
+      </c>
+      <c r="V73">
+        <v>0.3</v>
+      </c>
+      <c r="W73">
+        <v>0.03206</v>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y73">
+        <v>10.58206974930021</v>
+      </c>
+      <c r="Z73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74">
+        <v>0.72</v>
+      </c>
+      <c r="B74">
+        <v>0.116672488949289</v>
+      </c>
+      <c r="C74">
+        <v>11.50260287046755</v>
+      </c>
+      <c r="D74">
+        <v>32.88660287046755</v>
+      </c>
+      <c r="E74">
+        <v>21.384</v>
+      </c>
+      <c r="F74">
+        <v>21.384</v>
+      </c>
+      <c r="G74">
+        <v>0</v>
+      </c>
+      <c r="H74">
+        <v>29.7</v>
+      </c>
+      <c r="I74">
+        <v>0</v>
+      </c>
+      <c r="J74">
+        <v>15.2</v>
+      </c>
+      <c r="K74">
+        <v>4.98</v>
+      </c>
+      <c r="L74">
+        <v>10.22</v>
+      </c>
+      <c r="M74">
+        <v>0.9793872</v>
+      </c>
+      <c r="N74">
+        <v>9.240612799999999</v>
+      </c>
+      <c r="O74">
+        <v>2.77218384</v>
+      </c>
+      <c r="P74">
+        <v>6.468428959999999</v>
+      </c>
+      <c r="Q74">
+        <v>11.44842896</v>
+      </c>
+      <c r="R74">
+        <v>2.571428571428571</v>
+      </c>
+      <c r="S74">
+        <v>0.3342474605331749</v>
+      </c>
+      <c r="T74">
+        <v>2.094534133108247</v>
+      </c>
+      <c r="U74">
+        <v>0.0458</v>
+      </c>
+      <c r="V74">
+        <v>0.3</v>
+      </c>
+      <c r="W74">
+        <v>0.03206</v>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y74">
+        <v>10.4350965583377</v>
+      </c>
+      <c r="Z74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75">
+        <v>0.73</v>
+      </c>
+      <c r="B75">
+        <v>0.1162885380987177</v>
+      </c>
+      <c r="C75">
+        <v>11.25468299671996</v>
+      </c>
+      <c r="D75">
+        <v>32.93568299671995</v>
+      </c>
+      <c r="E75">
+        <v>21.681</v>
+      </c>
+      <c r="F75">
+        <v>21.681</v>
+      </c>
+      <c r="G75">
+        <v>0</v>
+      </c>
+      <c r="H75">
+        <v>29.7</v>
+      </c>
+      <c r="I75">
+        <v>0</v>
+      </c>
+      <c r="J75">
+        <v>15.2</v>
+      </c>
+      <c r="K75">
+        <v>4.98</v>
+      </c>
+      <c r="L75">
+        <v>10.22</v>
+      </c>
+      <c r="M75">
+        <v>0.9929897999999999</v>
+      </c>
+      <c r="N75">
+        <v>9.227010199999999</v>
+      </c>
+      <c r="O75">
+        <v>2.76810306</v>
+      </c>
+      <c r="P75">
+        <v>6.458907139999999</v>
+      </c>
+      <c r="Q75">
+        <v>11.43890714</v>
+      </c>
+      <c r="R75">
+        <v>2.703703703703703</v>
+      </c>
+      <c r="S75">
+        <v>0.3440175485137694</v>
+      </c>
+      <c r="T75">
+        <v>2.163797827986165</v>
+      </c>
+      <c r="U75">
+        <v>0.0458</v>
+      </c>
+      <c r="V75">
+        <v>0.3</v>
+      </c>
+      <c r="W75">
+        <v>0.03206</v>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y75">
+        <v>10.2921500301413</v>
+      </c>
+      <c r="Z75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76">
+        <v>0.74</v>
+      </c>
+      <c r="B76">
+        <v>0.1159045872481465</v>
+      </c>
+      <c r="C76">
+        <v>11.00690983676754</v>
+      </c>
+      <c r="D76">
+        <v>32.98490983676754</v>
+      </c>
+      <c r="E76">
+        <v>21.978</v>
+      </c>
+      <c r="F76">
+        <v>21.978</v>
+      </c>
+      <c r="G76">
+        <v>0</v>
+      </c>
+      <c r="H76">
+        <v>29.7</v>
+      </c>
+      <c r="I76">
+        <v>0</v>
+      </c>
+      <c r="J76">
+        <v>15.2</v>
+      </c>
+      <c r="K76">
+        <v>4.98</v>
+      </c>
+      <c r="L76">
+        <v>10.22</v>
+      </c>
+      <c r="M76">
+        <v>1.0065924</v>
+      </c>
+      <c r="N76">
+        <v>9.213407599999998</v>
+      </c>
+      <c r="O76">
+        <v>2.764022279999999</v>
+      </c>
+      <c r="P76">
+        <v>6.449385319999999</v>
+      </c>
+      <c r="Q76">
+        <v>11.42938532</v>
+      </c>
+      <c r="R76">
+        <v>2.846153846153846</v>
+      </c>
+      <c r="S76">
+        <v>0.3545391817236402</v>
+      </c>
+      <c r="T76">
+        <v>2.238389499393154</v>
+      </c>
+      <c r="U76">
+        <v>0.0458</v>
+      </c>
+      <c r="V76">
+        <v>0.3</v>
+      </c>
+      <c r="W76">
+        <v>0.03206</v>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y76">
+        <v>10.15306692162587</v>
+      </c>
+      <c r="Z76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77">
+        <v>0.75</v>
+      </c>
+      <c r="B77">
+        <v>0.1155206363975752</v>
+      </c>
+      <c r="C77">
+        <v>10.75928404944595</v>
+      </c>
+      <c r="D77">
+        <v>33.03428404944595</v>
+      </c>
+      <c r="E77">
+        <v>22.275</v>
+      </c>
+      <c r="F77">
+        <v>22.275</v>
+      </c>
+      <c r="G77">
+        <v>0</v>
+      </c>
+      <c r="H77">
+        <v>29.7</v>
+      </c>
+      <c r="I77">
+        <v>0</v>
+      </c>
+      <c r="J77">
+        <v>15.2</v>
+      </c>
+      <c r="K77">
+        <v>4.98</v>
+      </c>
+      <c r="L77">
+        <v>10.22</v>
+      </c>
+      <c r="M77">
+        <v>1.020195</v>
+      </c>
+      <c r="N77">
+        <v>9.199805</v>
+      </c>
+      <c r="O77">
+        <v>2.7599415</v>
+      </c>
+      <c r="P77">
+        <v>6.4398635</v>
+      </c>
+      <c r="Q77">
+        <v>11.4198635</v>
+      </c>
+      <c r="R77">
+        <v>3</v>
+      </c>
+      <c r="S77">
+        <v>0.3659025455903008</v>
+      </c>
+      <c r="T77">
+        <v>2.318948504512702</v>
+      </c>
+      <c r="U77">
+        <v>0.0458</v>
+      </c>
+      <c r="V77">
+        <v>0.3</v>
+      </c>
+      <c r="W77">
+        <v>0.03206</v>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y77">
+        <v>10.01769269600419</v>
+      </c>
+      <c r="Z77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78">
+        <v>0.76</v>
+      </c>
+      <c r="B78">
+        <v>0.1163070855470039</v>
+      </c>
+      <c r="C78">
+        <v>10.36130872424645</v>
+      </c>
+      <c r="D78">
+        <v>32.93330872424645</v>
+      </c>
+      <c r="E78">
+        <v>22.572</v>
+      </c>
+      <c r="F78">
+        <v>22.572</v>
+      </c>
+      <c r="G78">
+        <v>0</v>
+      </c>
+      <c r="H78">
+        <v>29.7</v>
+      </c>
+      <c r="I78">
+        <v>0</v>
+      </c>
+      <c r="J78">
+        <v>15.2</v>
+      </c>
+      <c r="K78">
+        <v>4.98</v>
+      </c>
+      <c r="L78">
+        <v>10.22</v>
+      </c>
+      <c r="M78">
+        <v>1.083456</v>
+      </c>
+      <c r="N78">
+        <v>9.136543999999999</v>
+      </c>
+      <c r="O78">
+        <v>2.740963199999999</v>
+      </c>
+      <c r="P78">
+        <v>6.395580799999999</v>
+      </c>
+      <c r="Q78">
+        <v>11.3755808</v>
+      </c>
+      <c r="R78">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="S78">
+        <v>0.3782128564458498</v>
+      </c>
+      <c r="T78">
+        <v>2.406220760058879</v>
+      </c>
+      <c r="U78">
+        <v>0.048</v>
+      </c>
+      <c r="V78">
+        <v>0.3</v>
+      </c>
+      <c r="W78">
+        <v>0.0336</v>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y78">
+        <v>9.432778073128949</v>
+      </c>
+      <c r="Z78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79">
+        <v>0.77</v>
+      </c>
+      <c r="B79">
+        <v>0.1159385346964327</v>
+      </c>
+      <c r="C79">
+        <v>10.11155146072014</v>
+      </c>
+      <c r="D79">
+        <v>32.98055146072014</v>
+      </c>
+      <c r="E79">
+        <v>22.869</v>
+      </c>
+      <c r="F79">
+        <v>22.869</v>
+      </c>
+      <c r="G79">
+        <v>0</v>
+      </c>
+      <c r="H79">
+        <v>29.7</v>
+      </c>
+      <c r="I79">
+        <v>0</v>
+      </c>
+      <c r="J79">
+        <v>15.2</v>
+      </c>
+      <c r="K79">
+        <v>4.98</v>
+      </c>
+      <c r="L79">
+        <v>10.22</v>
+      </c>
+      <c r="M79">
+        <v>1.097712</v>
+      </c>
+      <c r="N79">
+        <v>9.122287999999999</v>
+      </c>
+      <c r="O79">
+        <v>2.7366864</v>
+      </c>
+      <c r="P79">
+        <v>6.385601599999999</v>
+      </c>
+      <c r="Q79">
+        <v>11.3656016</v>
+      </c>
+      <c r="R79">
+        <v>3.347826086956522</v>
+      </c>
+      <c r="S79">
+        <v>0.3915936291149247</v>
+      </c>
+      <c r="T79">
+        <v>2.50108190739168</v>
+      </c>
+      <c r="U79">
+        <v>0.048</v>
+      </c>
+      <c r="V79">
+        <v>0.3</v>
+      </c>
+      <c r="W79">
+        <v>0.0336</v>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y79">
+        <v>9.310274461789612</v>
+      </c>
+      <c r="Z79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80">
+        <v>0.78</v>
+      </c>
+      <c r="B80">
+        <v>0.1155699838458614</v>
+      </c>
+      <c r="C80">
+        <v>9.861929931042337</v>
+      </c>
+      <c r="D80">
+        <v>33.02792993104234</v>
+      </c>
+      <c r="E80">
+        <v>23.166</v>
+      </c>
+      <c r="F80">
+        <v>23.166</v>
+      </c>
+      <c r="G80">
+        <v>0</v>
+      </c>
+      <c r="H80">
+        <v>29.7</v>
+      </c>
+      <c r="I80">
+        <v>0</v>
+      </c>
+      <c r="J80">
+        <v>15.2</v>
+      </c>
+      <c r="K80">
+        <v>4.98</v>
+      </c>
+      <c r="L80">
+        <v>10.22</v>
+      </c>
+      <c r="M80">
+        <v>1.111968</v>
+      </c>
+      <c r="N80">
+        <v>9.108031999999998</v>
+      </c>
+      <c r="O80">
+        <v>2.732409599999999</v>
+      </c>
+      <c r="P80">
+        <v>6.375622399999999</v>
+      </c>
+      <c r="Q80">
+        <v>11.3556224</v>
+      </c>
+      <c r="R80">
+        <v>3.545454545454546</v>
+      </c>
+      <c r="S80">
+        <v>0.4061908356630065</v>
+      </c>
+      <c r="T80">
+        <v>2.604566795391099</v>
+      </c>
+      <c r="U80">
+        <v>0.048</v>
+      </c>
+      <c r="V80">
+        <v>0.3</v>
+      </c>
+      <c r="W80">
+        <v>0.0336</v>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y80">
+        <v>9.190911968689743</v>
+      </c>
+      <c r="Z80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81">
+        <v>0.79</v>
+      </c>
+      <c r="B81">
+        <v>0.1152014329952902</v>
+      </c>
+      <c r="C81">
+        <v>9.612444721023181</v>
+      </c>
+      <c r="D81">
+        <v>33.07544472102318</v>
+      </c>
+      <c r="E81">
+        <v>23.463</v>
+      </c>
+      <c r="F81">
+        <v>23.463</v>
+      </c>
+      <c r="G81">
+        <v>0</v>
+      </c>
+      <c r="H81">
+        <v>29.7</v>
+      </c>
+      <c r="I81">
+        <v>0</v>
+      </c>
+      <c r="J81">
+        <v>15.2</v>
+      </c>
+      <c r="K81">
+        <v>4.98</v>
+      </c>
+      <c r="L81">
+        <v>10.22</v>
+      </c>
+      <c r="M81">
+        <v>1.126224</v>
+      </c>
+      <c r="N81">
+        <v>9.093775999999998</v>
+      </c>
+      <c r="O81">
+        <v>2.7281328</v>
+      </c>
+      <c r="P81">
+        <v>6.365643199999999</v>
+      </c>
+      <c r="Q81">
+        <v>11.3456432</v>
+      </c>
+      <c r="R81">
+        <v>3.761904761904763</v>
+      </c>
+      <c r="S81">
+        <v>0.4221782523585247</v>
+      </c>
+      <c r="T81">
+        <v>2.717907387009511</v>
+      </c>
+      <c r="U81">
+        <v>0.048</v>
+      </c>
+      <c r="V81">
+        <v>0.3</v>
+      </c>
+      <c r="W81">
+        <v>0.0336</v>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y81">
+        <v>9.074571310858229</v>
+      </c>
+      <c r="Z81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82">
+        <v>0.8</v>
+      </c>
+      <c r="B82">
+        <v>0.1148328821447189</v>
+      </c>
+      <c r="C82">
+        <v>9.363096419848706</v>
+      </c>
+      <c r="D82">
+        <v>33.12309641984871</v>
+      </c>
+      <c r="E82">
+        <v>23.76</v>
+      </c>
+      <c r="F82">
+        <v>23.76</v>
+      </c>
+      <c r="G82">
+        <v>0</v>
+      </c>
+      <c r="H82">
+        <v>29.7</v>
+      </c>
+      <c r="I82">
+        <v>0</v>
+      </c>
+      <c r="J82">
+        <v>15.2</v>
+      </c>
+      <c r="K82">
+        <v>4.98</v>
+      </c>
+      <c r="L82">
+        <v>10.22</v>
+      </c>
+      <c r="M82">
+        <v>1.14048</v>
+      </c>
+      <c r="N82">
+        <v>9.079519999999999</v>
+      </c>
+      <c r="O82">
+        <v>2.723856</v>
+      </c>
+      <c r="P82">
+        <v>6.355663999999999</v>
+      </c>
+      <c r="Q82">
+        <v>11.335664</v>
+      </c>
+      <c r="R82">
+        <v>4.000000000000001</v>
+      </c>
+      <c r="S82">
+        <v>0.4397644107235946</v>
+      </c>
+      <c r="T82">
+        <v>2.842582037789764</v>
+      </c>
+      <c r="U82">
+        <v>0.048</v>
+      </c>
+      <c r="V82">
+        <v>0.3</v>
+      </c>
+      <c r="W82">
+        <v>0.0336</v>
+      </c>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y82">
+        <v>8.961139169472499</v>
+      </c>
+      <c r="Z82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="B83">
+        <v>0.1144643312941477</v>
+      </c>
+      <c r="C83">
+        <v>9.113885620105179</v>
+      </c>
+      <c r="D83">
+        <v>33.17088562010518</v>
+      </c>
+      <c r="E83">
+        <v>24.057</v>
+      </c>
+      <c r="F83">
+        <v>24.057</v>
+      </c>
+      <c r="G83">
+        <v>0</v>
+      </c>
+      <c r="H83">
+        <v>29.7</v>
+      </c>
+      <c r="I83">
+        <v>0</v>
+      </c>
+      <c r="J83">
+        <v>15.2</v>
+      </c>
+      <c r="K83">
+        <v>4.98</v>
+      </c>
+      <c r="L83">
+        <v>10.22</v>
+      </c>
+      <c r="M83">
+        <v>1.154736</v>
+      </c>
+      <c r="N83">
+        <v>9.065263999999999</v>
+      </c>
+      <c r="O83">
+        <v>2.7195792</v>
+      </c>
+      <c r="P83">
+        <v>6.345684799999999</v>
+      </c>
+      <c r="Q83">
+        <v>11.3256848</v>
+      </c>
+      <c r="R83">
+        <v>4.263157894736843</v>
+      </c>
+      <c r="S83">
+        <v>0.4592017436534088</v>
+      </c>
+      <c r="T83">
+        <v>2.98038033602057</v>
+      </c>
+      <c r="U83">
+        <v>0.048</v>
+      </c>
+      <c r="V83">
+        <v>0.3</v>
+      </c>
+      <c r="W83">
+        <v>0.0336</v>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y83">
+        <v>8.850507821701235</v>
+      </c>
+      <c r="Z83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84">
+        <v>0.8200000000000001</v>
+      </c>
+      <c r="B84">
+        <v>0.1140957804435764</v>
+      </c>
+      <c r="C84">
+        <v>8.864812917803722</v>
+      </c>
+      <c r="D84">
+        <v>33.21881291780372</v>
+      </c>
+      <c r="E84">
+        <v>24.354</v>
+      </c>
+      <c r="F84">
+        <v>24.354</v>
+      </c>
+      <c r="G84">
+        <v>0</v>
+      </c>
+      <c r="H84">
+        <v>29.7</v>
+      </c>
+      <c r="I84">
+        <v>0</v>
+      </c>
+      <c r="J84">
+        <v>15.2</v>
+      </c>
+      <c r="K84">
+        <v>4.98</v>
+      </c>
+      <c r="L84">
+        <v>10.22</v>
+      </c>
+      <c r="M84">
+        <v>1.168992</v>
+      </c>
+      <c r="N84">
+        <v>9.051007999999999</v>
+      </c>
+      <c r="O84">
+        <v>2.7153024</v>
+      </c>
+      <c r="P84">
+        <v>6.3357056</v>
+      </c>
+      <c r="Q84">
+        <v>11.3157056</v>
+      </c>
+      <c r="R84">
+        <v>4.555555555555557</v>
+      </c>
+      <c r="S84">
+        <v>0.4807987802420912</v>
+      </c>
+      <c r="T84">
+        <v>3.133489556277021</v>
+      </c>
+      <c r="U84">
+        <v>0.048</v>
+      </c>
+      <c r="V84">
+        <v>0.3</v>
+      </c>
+      <c r="W84">
+        <v>0.0336</v>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y84">
+        <v>8.742574799485366</v>
+      </c>
+      <c r="Z84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85">
+        <v>0.8300000000000001</v>
+      </c>
+      <c r="B85">
+        <v>0.1137272295930051</v>
+      </c>
+      <c r="C85">
+        <v>8.615878912405012</v>
+      </c>
+      <c r="D85">
+        <v>33.26687891240501</v>
+      </c>
+      <c r="E85">
+        <v>24.651</v>
+      </c>
+      <c r="F85">
+        <v>24.651</v>
+      </c>
+      <c r="G85">
+        <v>0</v>
+      </c>
+      <c r="H85">
+        <v>29.7</v>
+      </c>
+      <c r="I85">
+        <v>0</v>
+      </c>
+      <c r="J85">
+        <v>15.2</v>
+      </c>
+      <c r="K85">
+        <v>4.98</v>
+      </c>
+      <c r="L85">
+        <v>10.22</v>
+      </c>
+      <c r="M85">
+        <v>1.183248</v>
+      </c>
+      <c r="N85">
+        <v>9.036751999999998</v>
+      </c>
+      <c r="O85">
+        <v>2.711025599999999</v>
+      </c>
+      <c r="P85">
+        <v>6.325726399999999</v>
+      </c>
+      <c r="Q85">
+        <v>11.3057264</v>
+      </c>
+      <c r="R85">
+        <v>4.882352941176473</v>
+      </c>
+      <c r="S85">
+        <v>0.5049366446647363</v>
+      </c>
+      <c r="T85">
+        <v>3.304611625975407</v>
+      </c>
+      <c r="U85">
+        <v>0.048</v>
+      </c>
+      <c r="V85">
+        <v>0.3</v>
+      </c>
+      <c r="W85">
+        <v>0.0336</v>
+      </c>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y85">
+        <v>8.637242572985542</v>
+      </c>
+      <c r="Z85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86">
+        <v>0.84</v>
+      </c>
+      <c r="B86">
+        <v>0.1133586787424339</v>
+      </c>
+      <c r="C86">
+        <v>8.367084206844343</v>
+      </c>
+      <c r="D86">
+        <v>33.31508420684434</v>
+      </c>
+      <c r="E86">
+        <v>24.948</v>
+      </c>
+      <c r="F86">
+        <v>24.948</v>
+      </c>
+      <c r="G86">
+        <v>0</v>
+      </c>
+      <c r="H86">
+        <v>29.7</v>
+      </c>
+      <c r="I86">
+        <v>0</v>
+      </c>
+      <c r="J86">
+        <v>15.2</v>
+      </c>
+      <c r="K86">
+        <v>4.98</v>
+      </c>
+      <c r="L86">
+        <v>10.22</v>
+      </c>
+      <c r="M86">
+        <v>1.197504</v>
+      </c>
+      <c r="N86">
+        <v>9.022495999999999</v>
+      </c>
+      <c r="O86">
+        <v>2.706748799999999</v>
+      </c>
+      <c r="P86">
+        <v>6.315747199999999</v>
+      </c>
+      <c r="Q86">
+        <v>11.2957472</v>
+      </c>
+      <c r="R86">
+        <v>5.249999999999999</v>
+      </c>
+      <c r="S86">
+        <v>0.5320917421402116</v>
+      </c>
+      <c r="T86">
+        <v>3.49712395438609</v>
+      </c>
+      <c r="U86">
+        <v>0.048</v>
+      </c>
+      <c r="V86">
+        <v>0.3</v>
+      </c>
+      <c r="W86">
+        <v>0.0336</v>
+      </c>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y86">
+        <v>8.534418256640478</v>
+      </c>
+      <c r="Z86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87">
+        <v>0.85</v>
+      </c>
+      <c r="B87">
+        <v>0.1129901278918626</v>
+      </c>
+      <c r="C87">
+        <v>8.118429407556796</v>
+      </c>
+      <c r="D87">
+        <v>33.36342940755679</v>
+      </c>
+      <c r="E87">
+        <v>25.245</v>
+      </c>
+      <c r="F87">
+        <v>25.245</v>
+      </c>
+      <c r="G87">
+        <v>0</v>
+      </c>
+      <c r="H87">
+        <v>29.7</v>
+      </c>
+      <c r="I87">
+        <v>0</v>
+      </c>
+      <c r="J87">
+        <v>15.2</v>
+      </c>
+      <c r="K87">
+        <v>4.98</v>
+      </c>
+      <c r="L87">
+        <v>10.22</v>
+      </c>
+      <c r="M87">
+        <v>1.21176</v>
+      </c>
+      <c r="N87">
+        <v>9.008239999999999</v>
+      </c>
+      <c r="O87">
+        <v>2.702472</v>
+      </c>
+      <c r="P87">
+        <v>6.305767999999999</v>
+      </c>
+      <c r="Q87">
+        <v>11.285768</v>
+      </c>
+      <c r="R87">
+        <v>5.666666666666666</v>
+      </c>
+      <c r="S87">
+        <v>0.562867519279084</v>
+      </c>
+      <c r="T87">
+        <v>3.715304593251533</v>
+      </c>
+      <c r="U87">
+        <v>0.048</v>
+      </c>
+      <c r="V87">
+        <v>0.3</v>
+      </c>
+      <c r="W87">
+        <v>0.0336</v>
+      </c>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y87">
+        <v>8.43401333597412</v>
+      </c>
+      <c r="Z87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88">
+        <v>0.86</v>
+      </c>
+      <c r="B88">
+        <v>0.1126215770412913</v>
+      </c>
+      <c r="C88">
+        <v>7.869915124502686</v>
+      </c>
+      <c r="D88">
+        <v>33.41191512450268</v>
+      </c>
+      <c r="E88">
+        <v>25.542</v>
+      </c>
+      <c r="F88">
+        <v>25.542</v>
+      </c>
+      <c r="G88">
+        <v>0</v>
+      </c>
+      <c r="H88">
+        <v>29.7</v>
+      </c>
+      <c r="I88">
+        <v>0</v>
+      </c>
+      <c r="J88">
+        <v>15.2</v>
+      </c>
+      <c r="K88">
+        <v>4.98</v>
+      </c>
+      <c r="L88">
+        <v>10.22</v>
+      </c>
+      <c r="M88">
+        <v>1.226016</v>
+      </c>
+      <c r="N88">
+        <v>8.993983999999999</v>
+      </c>
+      <c r="O88">
+        <v>2.6981952</v>
+      </c>
+      <c r="P88">
+        <v>6.2957888</v>
+      </c>
+      <c r="Q88">
+        <v>11.2757888</v>
+      </c>
+      <c r="R88">
+        <v>6.142857142857142</v>
+      </c>
+      <c r="S88">
+        <v>0.5980398360092238</v>
+      </c>
+      <c r="T88">
+        <v>3.964653894812038</v>
+      </c>
+      <c r="U88">
+        <v>0.048</v>
+      </c>
+      <c r="V88">
+        <v>0.3</v>
+      </c>
+      <c r="W88">
+        <v>0.0336</v>
+      </c>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y88">
+        <v>8.335943413462793</v>
+      </c>
+      <c r="Z88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89">
+        <v>0.87</v>
+      </c>
+      <c r="B89">
+        <v>0.1122530261907201</v>
+      </c>
+      <c r="C89">
+        <v>7.621541971193203</v>
+      </c>
+      <c r="D89">
+        <v>33.4605419711932</v>
+      </c>
+      <c r="E89">
+        <v>25.839</v>
+      </c>
+      <c r="F89">
+        <v>25.839</v>
+      </c>
+      <c r="G89">
+        <v>0</v>
+      </c>
+      <c r="H89">
+        <v>29.7</v>
+      </c>
+      <c r="I89">
+        <v>0</v>
+      </c>
+      <c r="J89">
+        <v>15.2</v>
+      </c>
+      <c r="K89">
+        <v>4.98</v>
+      </c>
+      <c r="L89">
+        <v>10.22</v>
+      </c>
+      <c r="M89">
+        <v>1.240272</v>
+      </c>
+      <c r="N89">
+        <v>8.979727999999998</v>
+      </c>
+      <c r="O89">
+        <v>2.693918399999999</v>
+      </c>
+      <c r="P89">
+        <v>6.285809599999999</v>
+      </c>
+      <c r="Q89">
+        <v>11.2658096</v>
+      </c>
+      <c r="R89">
+        <v>6.692307692307692</v>
+      </c>
+      <c r="S89">
+        <v>0.6386232783901546</v>
+      </c>
+      <c r="T89">
+        <v>4.252364627381853</v>
+      </c>
+      <c r="U89">
+        <v>0.048</v>
+      </c>
+      <c r="V89">
+        <v>0.3</v>
+      </c>
+      <c r="W89">
+        <v>0.0336</v>
+      </c>
+      <c r="X89" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y89">
+        <v>8.240127971928736</v>
+      </c>
+      <c r="Z89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90">
+        <v>0.88</v>
+      </c>
+      <c r="B90">
+        <v>0.1118844753401488</v>
+      </c>
+      <c r="C90">
+        <v>7.373310564716316</v>
+      </c>
+      <c r="D90">
+        <v>33.50931056471632</v>
+      </c>
+      <c r="E90">
+        <v>26.136</v>
+      </c>
+      <c r="F90">
+        <v>26.136</v>
+      </c>
+      <c r="G90">
+        <v>0</v>
+      </c>
+      <c r="H90">
+        <v>29.7</v>
+      </c>
+      <c r="I90">
+        <v>0</v>
+      </c>
+      <c r="J90">
+        <v>15.2</v>
+      </c>
+      <c r="K90">
+        <v>4.98</v>
+      </c>
+      <c r="L90">
+        <v>10.22</v>
+      </c>
+      <c r="M90">
+        <v>1.254528</v>
+      </c>
+      <c r="N90">
+        <v>8.965471999999998</v>
+      </c>
+      <c r="O90">
+        <v>2.689641599999999</v>
+      </c>
+      <c r="P90">
+        <v>6.275830399999998</v>
+      </c>
+      <c r="Q90">
+        <v>11.2558304</v>
+      </c>
+      <c r="R90">
+        <v>7.333333333333334</v>
+      </c>
+      <c r="S90">
+        <v>0.6859706278345736</v>
+      </c>
+      <c r="T90">
+        <v>4.588027148713303</v>
+      </c>
+      <c r="U90">
+        <v>0.048</v>
+      </c>
+      <c r="V90">
+        <v>0.3</v>
+      </c>
+      <c r="W90">
+        <v>0.0336</v>
+      </c>
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y90">
+        <v>8.146490154065908</v>
+      </c>
+      <c r="Z90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91">
+        <v>0.89</v>
+      </c>
+      <c r="B91">
+        <v>0.1115159244895776</v>
+      </c>
+      <c r="C91">
+        <v>7.125221525762825</v>
+      </c>
+      <c r="D91">
+        <v>33.55822152576282</v>
+      </c>
+      <c r="E91">
+        <v>26.433</v>
+      </c>
+      <c r="F91">
+        <v>26.433</v>
+      </c>
+      <c r="G91">
+        <v>0</v>
+      </c>
+      <c r="H91">
+        <v>29.7</v>
+      </c>
+      <c r="I91">
+        <v>0</v>
+      </c>
+      <c r="J91">
+        <v>15.2</v>
+      </c>
+      <c r="K91">
+        <v>4.98</v>
+      </c>
+      <c r="L91">
+        <v>10.22</v>
+      </c>
+      <c r="M91">
+        <v>1.268784</v>
+      </c>
+      <c r="N91">
+        <v>8.951215999999999</v>
+      </c>
+      <c r="O91">
+        <v>2.685364799999999</v>
+      </c>
+      <c r="P91">
+        <v>6.265851199999999</v>
+      </c>
+      <c r="Q91">
+        <v>11.2458512</v>
+      </c>
+      <c r="R91">
+        <v>8.090909090909092</v>
+      </c>
+      <c r="S91">
+        <v>0.7419265862688873</v>
+      </c>
+      <c r="T91">
+        <v>4.984719219377745</v>
+      </c>
+      <c r="U91">
+        <v>0.048</v>
+      </c>
+      <c r="V91">
+        <v>0.3</v>
+      </c>
+      <c r="W91">
+        <v>0.0336</v>
+      </c>
+      <c r="X91" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y91">
+        <v>8.054956556829215</v>
+      </c>
+      <c r="Z91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92">
+        <v>0.9</v>
+      </c>
+      <c r="B92">
+        <v>0.1111473736390063</v>
+      </c>
+      <c r="C92">
+        <v>6.877275478652773</v>
+      </c>
+      <c r="D92">
+        <v>33.60727547865277</v>
+      </c>
+      <c r="E92">
+        <v>26.73</v>
+      </c>
+      <c r="F92">
+        <v>26.73</v>
+      </c>
+      <c r="G92">
+        <v>0</v>
+      </c>
+      <c r="H92">
+        <v>29.7</v>
+      </c>
+      <c r="I92">
+        <v>0</v>
+      </c>
+      <c r="J92">
+        <v>15.2</v>
+      </c>
+      <c r="K92">
+        <v>4.98</v>
+      </c>
+      <c r="L92">
+        <v>10.22</v>
+      </c>
+      <c r="M92">
+        <v>1.28304</v>
+      </c>
+      <c r="N92">
+        <v>8.936959999999999</v>
+      </c>
+      <c r="O92">
+        <v>2.681087999999999</v>
+      </c>
+      <c r="P92">
+        <v>6.255872</v>
+      </c>
+      <c r="Q92">
+        <v>11.235872</v>
+      </c>
+      <c r="R92">
+        <v>9.000000000000002</v>
+      </c>
+      <c r="S92">
+        <v>0.8090737363900633</v>
+      </c>
+      <c r="T92">
+        <v>5.460749704175074</v>
+      </c>
+      <c r="U92">
+        <v>0.048</v>
+      </c>
+      <c r="V92">
+        <v>0.3</v>
+      </c>
+      <c r="W92">
+        <v>0.0336</v>
+      </c>
+      <c r="X92" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y92">
+        <v>7.965457039531113</v>
+      </c>
+      <c r="Z92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93">
+        <v>0.91</v>
+      </c>
+      <c r="B93">
+        <v>0.1107788227884351</v>
+      </c>
+      <c r="C93">
+        <v>6.629473051361906</v>
+      </c>
+      <c r="D93">
+        <v>33.65647305136191</v>
+      </c>
+      <c r="E93">
+        <v>27.027</v>
+      </c>
+      <c r="F93">
+        <v>27.027</v>
+      </c>
+      <c r="G93">
+        <v>0</v>
+      </c>
+      <c r="H93">
+        <v>29.7</v>
+      </c>
+      <c r="I93">
+        <v>0</v>
+      </c>
+      <c r="J93">
+        <v>15.2</v>
+      </c>
+      <c r="K93">
+        <v>4.98</v>
+      </c>
+      <c r="L93">
+        <v>10.22</v>
+      </c>
+      <c r="M93">
+        <v>1.297296</v>
+      </c>
+      <c r="N93">
+        <v>8.922704</v>
+      </c>
+      <c r="O93">
+        <v>2.6768112</v>
+      </c>
+      <c r="P93">
+        <v>6.2458928</v>
+      </c>
+      <c r="Q93">
+        <v>11.2258928</v>
+      </c>
+      <c r="R93">
+        <v>10.11111111111111</v>
+      </c>
+      <c r="S93">
+        <v>0.8911424754270565</v>
+      </c>
+      <c r="T93">
+        <v>6.042564741149587</v>
+      </c>
+      <c r="U93">
+        <v>0.048</v>
+      </c>
+      <c r="V93">
+        <v>0.3</v>
+      </c>
+      <c r="W93">
+        <v>0.0336</v>
+      </c>
+      <c r="X93" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y93">
+        <v>7.87792454459121</v>
+      </c>
+      <c r="Z93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94">
+        <v>0.92</v>
+      </c>
+      <c r="B94">
+        <v>0.1104102719378638</v>
+      </c>
+      <c r="C94">
+        <v>6.381814875548567</v>
+      </c>
+      <c r="D94">
+        <v>33.70581487554857</v>
+      </c>
+      <c r="E94">
+        <v>27.324</v>
+      </c>
+      <c r="F94">
+        <v>27.324</v>
+      </c>
+      <c r="G94">
+        <v>0</v>
+      </c>
+      <c r="H94">
+        <v>29.7</v>
+      </c>
+      <c r="I94">
+        <v>0</v>
+      </c>
+      <c r="J94">
+        <v>15.2</v>
+      </c>
+      <c r="K94">
+        <v>4.98</v>
+      </c>
+      <c r="L94">
+        <v>10.22</v>
+      </c>
+      <c r="M94">
+        <v>1.311552</v>
+      </c>
+      <c r="N94">
+        <v>8.908447999999998</v>
+      </c>
+      <c r="O94">
+        <v>2.6725344</v>
+      </c>
+      <c r="P94">
+        <v>6.235913599999998</v>
+      </c>
+      <c r="Q94">
+        <v>11.2159136</v>
+      </c>
+      <c r="R94">
+        <v>11.50000000000001</v>
+      </c>
+      <c r="S94">
+        <v>0.9937283992232979</v>
+      </c>
+      <c r="T94">
+        <v>6.76983353736773</v>
+      </c>
+      <c r="U94">
+        <v>0.048</v>
+      </c>
+      <c r="V94">
+        <v>0.3</v>
+      </c>
+      <c r="W94">
+        <v>0.0336</v>
+      </c>
+      <c r="X94" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y94">
+        <v>7.792294929976087</v>
+      </c>
+      <c r="Z94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95">
+        <v>0.93</v>
+      </c>
+      <c r="B95">
+        <v>0.1110182210872925</v>
+      </c>
+      <c r="C95">
+        <v>6.003499576179905</v>
+      </c>
+      <c r="D95">
+        <v>33.62449957617991</v>
+      </c>
+      <c r="E95">
+        <v>27.621</v>
+      </c>
+      <c r="F95">
+        <v>27.621</v>
+      </c>
+      <c r="G95">
+        <v>0</v>
+      </c>
+      <c r="H95">
+        <v>29.7</v>
+      </c>
+      <c r="I95">
+        <v>0</v>
+      </c>
+      <c r="J95">
+        <v>15.2</v>
+      </c>
+      <c r="K95">
+        <v>4.98</v>
+      </c>
+      <c r="L95">
+        <v>10.22</v>
+      </c>
+      <c r="M95">
+        <v>1.3672395</v>
+      </c>
+      <c r="N95">
+        <v>8.852760499999999</v>
+      </c>
+      <c r="O95">
+        <v>2.65582815</v>
+      </c>
+      <c r="P95">
+        <v>6.196932349999999</v>
+      </c>
+      <c r="Q95">
+        <v>11.17693235</v>
+      </c>
+      <c r="R95">
+        <v>13.2857142857143</v>
+      </c>
+      <c r="S95">
+        <v>1.125624586961323</v>
+      </c>
+      <c r="T95">
+        <v>7.704893418219628</v>
+      </c>
+      <c r="U95">
+        <v>0.0495</v>
+      </c>
+      <c r="V95">
+        <v>0.3</v>
+      </c>
+      <c r="W95">
+        <v>0.03465</v>
+      </c>
+      <c r="X95" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y95">
+        <v>7.474915696920691</v>
+      </c>
+      <c r="Z95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96">
+        <v>0.9400000000000001</v>
+      </c>
+      <c r="B96">
+        <v>0.1106601702367213</v>
+      </c>
+      <c r="C96">
+        <v>5.754342555829208</v>
+      </c>
+      <c r="D96">
+        <v>33.67234255582921</v>
+      </c>
+      <c r="E96">
+        <v>27.918</v>
+      </c>
+      <c r="F96">
+        <v>27.918</v>
+      </c>
+      <c r="G96">
+        <v>0</v>
+      </c>
+      <c r="H96">
+        <v>29.7</v>
+      </c>
+      <c r="I96">
+        <v>0</v>
+      </c>
+      <c r="J96">
+        <v>15.2</v>
+      </c>
+      <c r="K96">
+        <v>4.98</v>
+      </c>
+      <c r="L96">
+        <v>10.22</v>
+      </c>
+      <c r="M96">
+        <v>1.381941</v>
+      </c>
+      <c r="N96">
+        <v>8.838058999999998</v>
+      </c>
+      <c r="O96">
+        <v>2.651417699999999</v>
+      </c>
+      <c r="P96">
+        <v>6.186641299999998</v>
+      </c>
+      <c r="Q96">
+        <v>11.1666413</v>
+      </c>
+      <c r="R96">
+        <v>15.66666666666668</v>
+      </c>
+      <c r="S96">
+        <v>1.301486170612022</v>
+      </c>
+      <c r="T96">
+        <v>8.951639926022159</v>
+      </c>
+      <c r="U96">
+        <v>0.0495</v>
+      </c>
+      <c r="V96">
+        <v>0.3</v>
+      </c>
+      <c r="W96">
+        <v>0.03465</v>
+      </c>
+      <c r="X96" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y96">
+        <v>7.395395317166215</v>
+      </c>
+      <c r="Z96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97">
+        <v>0.9500000000000001</v>
+      </c>
+      <c r="B97">
+        <v>0.11030211938615</v>
+      </c>
+      <c r="C97">
+        <v>5.505321877266748</v>
+      </c>
+      <c r="D97">
+        <v>33.72032187726675</v>
+      </c>
+      <c r="E97">
+        <v>28.215</v>
+      </c>
+      <c r="F97">
+        <v>28.215</v>
+      </c>
+      <c r="G97">
+        <v>0</v>
+      </c>
+      <c r="H97">
+        <v>29.7</v>
+      </c>
+      <c r="I97">
+        <v>0</v>
+      </c>
+      <c r="J97">
+        <v>15.2</v>
+      </c>
+      <c r="K97">
+        <v>4.98</v>
+      </c>
+      <c r="L97">
+        <v>10.22</v>
+      </c>
+      <c r="M97">
+        <v>1.3966425</v>
+      </c>
+      <c r="N97">
+        <v>8.823357499999998</v>
+      </c>
+      <c r="O97">
+        <v>2.647007249999999</v>
+      </c>
+      <c r="P97">
+        <v>6.176350249999999</v>
+      </c>
+      <c r="Q97">
+        <v>11.15635025</v>
+      </c>
+      <c r="R97">
+        <v>19.00000000000003</v>
+      </c>
+      <c r="S97">
+        <v>1.547692387723003</v>
+      </c>
+      <c r="T97">
+        <v>10.6970850369457</v>
+      </c>
+      <c r="U97">
+        <v>0.0495</v>
+      </c>
+      <c r="V97">
+        <v>0.3</v>
+      </c>
+      <c r="W97">
+        <v>0.03465</v>
+      </c>
+      <c r="X97" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y97">
+        <v>7.31754905066973</v>
+      </c>
+      <c r="Z97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98">
+        <v>0.96</v>
+      </c>
+      <c r="B98">
+        <v>0.1099440685355788</v>
+      </c>
+      <c r="C98">
+        <v>5.256438124139546</v>
+      </c>
+      <c r="D98">
+        <v>33.76843812413954</v>
+      </c>
+      <c r="E98">
+        <v>28.512</v>
+      </c>
+      <c r="F98">
+        <v>28.512</v>
+      </c>
+      <c r="G98">
+        <v>0</v>
+      </c>
+      <c r="H98">
+        <v>29.7</v>
+      </c>
+      <c r="I98">
+        <v>0</v>
+      </c>
+      <c r="J98">
+        <v>15.2</v>
+      </c>
+      <c r="K98">
+        <v>4.98</v>
+      </c>
+      <c r="L98">
+        <v>10.22</v>
+      </c>
+      <c r="M98">
+        <v>1.411344</v>
+      </c>
+      <c r="N98">
+        <v>8.808655999999999</v>
+      </c>
+      <c r="O98">
+        <v>2.6425968</v>
+      </c>
+      <c r="P98">
+        <v>6.166059199999999</v>
+      </c>
+      <c r="Q98">
+        <v>11.1460592</v>
+      </c>
+      <c r="R98">
+        <v>23.99999999999998</v>
+      </c>
+      <c r="S98">
+        <v>1.917001713389468</v>
+      </c>
+      <c r="T98">
+        <v>13.31525270333099</v>
+      </c>
+      <c r="U98">
+        <v>0.0495</v>
+      </c>
+      <c r="V98">
+        <v>0.3</v>
+      </c>
+      <c r="W98">
+        <v>0.03465</v>
+      </c>
+      <c r="X98" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y98">
+        <v>7.241324581391921</v>
+      </c>
+      <c r="Z98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99">
+        <v>0.97</v>
+      </c>
+      <c r="B99">
+        <v>0.1095860176850075</v>
+      </c>
+      <c r="C99">
+        <v>5.00769188343066</v>
+      </c>
+      <c r="D99">
+        <v>33.81669188343066</v>
+      </c>
+      <c r="E99">
+        <v>28.809</v>
+      </c>
+      <c r="F99">
+        <v>28.809</v>
+      </c>
+      <c r="G99">
+        <v>0</v>
+      </c>
+      <c r="H99">
+        <v>29.7</v>
+      </c>
+      <c r="I99">
+        <v>0</v>
+      </c>
+      <c r="J99">
+        <v>15.2</v>
+      </c>
+      <c r="K99">
+        <v>4.98</v>
+      </c>
+      <c r="L99">
+        <v>10.22</v>
+      </c>
+      <c r="M99">
+        <v>1.4260455</v>
+      </c>
+      <c r="N99">
+        <v>8.793954499999998</v>
+      </c>
+      <c r="O99">
+        <v>2.638186349999999</v>
+      </c>
+      <c r="P99">
+        <v>6.155768149999998</v>
+      </c>
+      <c r="Q99">
+        <v>11.13576815</v>
+      </c>
+      <c r="R99">
+        <v>32.33333333333331</v>
+      </c>
+      <c r="S99">
+        <v>2.532517256166916</v>
+      </c>
+      <c r="T99">
+        <v>17.67886548063984</v>
+      </c>
+      <c r="U99">
+        <v>0.0495</v>
+      </c>
+      <c r="V99">
+        <v>0.3</v>
+      </c>
+      <c r="W99">
+        <v>0.03465</v>
+      </c>
+      <c r="X99" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y99">
+        <v>7.166671750655921</v>
+      </c>
+      <c r="Z99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100">
+        <v>0.98</v>
+      </c>
+      <c r="B100">
+        <v>0.1092279668344363</v>
+      </c>
+      <c r="C100">
+        <v>4.75908374548305</v>
+      </c>
+      <c r="D100">
+        <v>33.86508374548305</v>
+      </c>
+      <c r="E100">
+        <v>29.106</v>
+      </c>
+      <c r="F100">
+        <v>29.106</v>
+      </c>
+      <c r="G100">
+        <v>0</v>
+      </c>
+      <c r="H100">
+        <v>29.7</v>
+      </c>
+      <c r="I100">
+        <v>0</v>
+      </c>
+      <c r="J100">
+        <v>15.2</v>
+      </c>
+      <c r="K100">
+        <v>4.98</v>
+      </c>
+      <c r="L100">
+        <v>10.22</v>
+      </c>
+      <c r="M100">
+        <v>1.440747</v>
+      </c>
+      <c r="N100">
+        <v>8.779252999999999</v>
+      </c>
+      <c r="O100">
+        <v>2.633775899999999</v>
+      </c>
+      <c r="P100">
+        <v>6.145477099999999</v>
+      </c>
+      <c r="Q100">
+        <v>11.1254771</v>
+      </c>
+      <c r="R100">
+        <v>48.99999999999996</v>
+      </c>
+      <c r="S100">
+        <v>3.76354834172181</v>
+      </c>
+      <c r="T100">
+        <v>26.40609103525752</v>
+      </c>
+      <c r="U100">
+        <v>0.0495</v>
+      </c>
+      <c r="V100">
+        <v>0.3</v>
+      </c>
+      <c r="W100">
+        <v>0.03465</v>
+      </c>
+      <c r="X100" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y100">
+        <v>7.0935424470778</v>
+      </c>
+      <c r="Z100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101">
+        <v>0.99</v>
+      </c>
+      <c r="B101">
+        <v>0.108869915983865</v>
+      </c>
+      <c r="C101">
+        <v>4.510614304023655</v>
+      </c>
+      <c r="D101">
+        <v>33.91361430402365</v>
+      </c>
+      <c r="E101">
+        <v>29.403</v>
+      </c>
+      <c r="F101">
+        <v>29.403</v>
+      </c>
+      <c r="G101">
+        <v>0</v>
+      </c>
+      <c r="H101">
+        <v>29.7</v>
+      </c>
+      <c r="I101">
+        <v>0</v>
+      </c>
+      <c r="J101">
+        <v>15.2</v>
+      </c>
+      <c r="K101">
+        <v>4.98</v>
+      </c>
+      <c r="L101">
+        <v>10.22</v>
+      </c>
+      <c r="M101">
+        <v>1.4554485</v>
+      </c>
+      <c r="N101">
+        <v>8.7645515</v>
+      </c>
+      <c r="O101">
+        <v>2.62936545</v>
+      </c>
+      <c r="P101">
+        <v>6.13518605</v>
+      </c>
+      <c r="Q101">
+        <v>11.11518605</v>
+      </c>
+      <c r="R101">
+        <v>98.99999999999991</v>
+      </c>
+      <c r="S101">
+        <v>7.456641598386494</v>
+      </c>
+      <c r="T101">
+        <v>52.58776769911059</v>
+      </c>
+      <c r="U101">
+        <v>0.0495</v>
+      </c>
+      <c r="V101">
+        <v>0.3</v>
+      </c>
+      <c r="W101">
+        <v>0.03465</v>
+      </c>
+      <c r="X101" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y101">
+        <v>7.021890503167924</v>
+      </c>
+      <c r="Z101">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
